--- a/argus/kship/models/017960_model.xlsx
+++ b/argus/kship/models/017960_model.xlsx
@@ -654,55 +654,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 174984억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 174986억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 184799억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 184874억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 191671억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 191819억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 188137억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 188633억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 187407억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 187969억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 185743억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 186298억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 183395억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 183945억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 175993억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 176262억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 163815억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 164085억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -918,31 +918,31 @@
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3003억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3004억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3368억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3371억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3652억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3655억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3798억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3802억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4094억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 4099억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1881,55 +1881,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 174984억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 174986억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 184799억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 184874억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 191671억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 191819억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 188137억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 188633억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 187407억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 187969억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 185743억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 186298억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 183395억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 183945억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 175993억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 176262억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 163815억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 164085억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2360,31 +2360,31 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3003억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3004억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3368억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3371억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3652억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3655억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3798억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3802억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4094억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 4099억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4703,7 +4703,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 11.1, "op_wape_pct": 63.7, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 2265.3, "rev_act": 2211.32, "op_pred": 152.37, "op_act": 298.63}, {"q": "2025Q4", "rev_pred": 2533.53, "rev_act": 2318.43, "op_pred": 170.41, "op_act": 383.37}, {"q": "2026Q1", "rev_pred": 1831.64, "rev_act": 2118.22, "op_pred": 123.2, "op_act": 410.66}, {"q": "2026Q2", "rev_pred": 1982.74, "rev_act": 2433.78, "op_pred": 133.36, "op_act": 504.0}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 11.1, "op_wape_pct": 63.7, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 2265.3, "rev_act": 2211.32, "op_pred": 152.37, "op_act": 298.63}, {"q": "2025Q4", "rev_pred": 2533.53, "rev_act": 2318.43, "op_pred": 170.41, "op_act": 383.37}, {"q": "2026Q1", "rev_pred": 1831.63, "rev_act": 2118.22, "op_pred": 123.2, "op_act": 410.66}, {"q": "2026Q2", "rev_pred": 1982.74, "rev_act": 2433.78, "op_pred": 133.36, "op_act": 504.0}]}</t>
         </is>
       </c>
     </row>
@@ -6754,33 +6754,33 @@
         <v>0.203118</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.448252</v>
+        <v>0.448265</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.302965</v>
+        <v>0.303503</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.307955</v>
+        <v>0.308966</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.164587</v>
+        <v>0.167654</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.070996</v>
+        <v>0.074197</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.005109</v>
+        <v>0.007696</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.043179</v>
+        <v>-0.041052</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.064554</v>
+        <v>-0.065578</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.125888</v>
+        <v>-0.127064</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6900,7 +6900,7 @@
         <v>0.095073</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.09507500000000001</v>
+        <v>0.09507400000000001</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
@@ -6910,13 +6910,13 @@
         <v>0.09507400000000001</v>
       </c>
       <c r="AG22" s="24" t="n">
+        <v>0.09507400000000001</v>
+      </c>
+      <c r="AH22" s="24" t="n">
+        <v>0.09507400000000001</v>
+      </c>
+      <c r="AI22" s="24" t="n">
         <v>0.09507500000000001</v>
-      </c>
-      <c r="AH22" s="24" t="n">
-        <v>0.09507599999999999</v>
-      </c>
-      <c r="AI22" s="24" t="n">
-        <v>0.09507400000000001</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
@@ -6929,10 +6929,10 @@
         <v>0.09507500000000001</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.09507500000000001</v>
+        <v>0.09507400000000001</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.09507400000000001</v>
+        <v>0.09507599999999999</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -7055,23 +7055,23 @@
         <v>0.137674</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.137673</v>
+        <v>0.137675</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.137676</v>
+        <v>0.137673</v>
       </c>
       <c r="AG23" s="24" t="n">
         <v>0.137673</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.137673</v>
+        <v>0.137675</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.137673</v>
+        <v>0.137675</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
@@ -7081,13 +7081,13 @@
         <v>0.137675</v>
       </c>
       <c r="AL23" s="24" t="n">
+        <v>0.137675</v>
+      </c>
+      <c r="AM23" s="24" t="n">
         <v>0.137674</v>
       </c>
-      <c r="AM23" s="24" t="n">
-        <v>0.137675</v>
-      </c>
       <c r="AN23" s="24" t="n">
-        <v>0.137675</v>
+        <v>0.137674</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7345,7 +7345,7 @@
         <v>4.82</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>5.5</v>
+        <v>5.51</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
@@ -7358,10 +7358,10 @@
         <v>6.92</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>7.88</v>
+        <v>7.89</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7794,39 +7794,39 @@
         <v>0.270009</v>
       </c>
       <c r="AD28" s="24" t="n">
-        <v>0.269999</v>
+        <v>0.269993</v>
       </c>
       <c r="AE28" s="25">
         <f>IFERROR(subQ!AE15/subQ!AE14,"")</f>
         <v/>
       </c>
       <c r="AF28" s="24" t="n">
-        <v>0.269995</v>
+        <v>0.269987</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.269995</v>
+        <v>0.269991</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.270005</v>
+        <v>0.269994</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.269991</v>
+        <v>0.270012</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ15/subQ!AJ14,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.269988</v>
+        <v>0.269994</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.269994</v>
+        <v>0.269993</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.270012</v>
+        <v>0.269993</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.270005</v>
+        <v>0.269995</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO15/subQ!AO14,"")</f>
@@ -8317,23 +8317,23 @@
       </c>
       <c r="AE32" s="30" t="n"/>
       <c r="AF32" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AG32" s="29" t="n">
         <v>165.37</v>
       </c>
       <c r="AH32" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AI32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AL32" s="29" t="n">
-        <v>165.37</v>
+        <v>165.36</v>
       </c>
       <c r="AM32" s="29" t="n">
         <v>0</v>
@@ -8445,23 +8445,23 @@
       </c>
       <c r="AE33" s="30" t="n"/>
       <c r="AF33" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AG33" s="29" t="n">
         <v>165.37</v>
       </c>
       <c r="AH33" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AI33" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AL33" s="29" t="n">
-        <v>165.37</v>
+        <v>165.36</v>
       </c>
       <c r="AM33" s="29" t="n">
         <v>0</v>
@@ -8697,33 +8697,33 @@
         <v>0.196624</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.207326</v>
+        <v>0.207332</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.141641</v>
+        <v>0.141696</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.0699</v>
+        <v>0.070007</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.130322</v>
+        <v>0.130642</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.133784</v>
+        <v>0.134121</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.09152</v>
+        <v>0.091724</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.043148</v>
+        <v>0.04338</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.08411200000000001</v>
+        <v>0.084144</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.084148</v>
+        <v>0.084188</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8829,29 +8829,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.124604</v>
+        <v>0.124653</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.062423</v>
+        <v>0.06252000000000001</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.117203</v>
+        <v>0.117492</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.121728</v>
+        <v>0.122043</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.084165</v>
+        <v>0.084357</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.039951</v>
+        <v>0.040168</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.07811899999999999</v>
+        <v>0.078155</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.078587</v>
+        <v>0.07863000000000001</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="AE42" s="25" t="n"/>
       <c r="AF42" s="24" t="n">
-        <v>-0.596949</v>
+        <v>-0.597441</v>
       </c>
       <c r="AG42" s="24" t="n">
         <v>-0.570922</v>
@@ -9496,20 +9496,20 @@
         <v>-0.085202</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>-0.116998</v>
+        <v>-0.118102</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>-0.025641</v>
+        <v>-0.026895</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.048406</v>
+        <v>-0.051948</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>0.001225</v>
+        <v>-0.001225</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>0.05875</v>
+        <v>0.057572</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -9622,7 +9622,7 @@
         <v>-0.133333</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>-0.121212</v>
+        <v>-0.128788</v>
       </c>
       <c r="AM43" s="24" t="n">
         <v>-0.11811</v>
@@ -9903,23 +9903,23 @@
         <v>0.137674</v>
       </c>
       <c r="AD45" s="24" t="n">
-        <v>0.137673</v>
+        <v>0.137675</v>
       </c>
       <c r="AE45" s="25">
         <f>IFERROR(subQ!AE36/subQ!AE35,"")</f>
         <v/>
       </c>
       <c r="AF45" s="24" t="n">
-        <v>0.137676</v>
+        <v>0.137673</v>
       </c>
       <c r="AG45" s="24" t="n">
         <v>0.137673</v>
       </c>
       <c r="AH45" s="24" t="n">
-        <v>0.137673</v>
+        <v>0.137675</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>0.137673</v>
+        <v>0.137675</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
@@ -9929,13 +9929,13 @@
         <v>0.137675</v>
       </c>
       <c r="AL45" s="24" t="n">
+        <v>0.137675</v>
+      </c>
+      <c r="AM45" s="24" t="n">
         <v>0.137674</v>
       </c>
-      <c r="AM45" s="24" t="n">
-        <v>0.137675</v>
-      </c>
       <c r="AN45" s="24" t="n">
-        <v>0.137675</v>
+        <v>0.137674</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>
@@ -41053,7 +41053,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2346.8</v>
+        <v>2347.5</v>
       </c>
     </row>
     <row r="30">

--- a/argus/kship/models/017960_model.xlsx
+++ b/argus/kship/models/017960_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$104</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$114</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$99</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -660,49 +660,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 184874억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 185433억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 191819억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 194470억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 188633억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 195664억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 187969억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 202208억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 186298억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 210338억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 183945억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 219550억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 176262억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 224410억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 164085억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 224982억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -906,43 +906,43 @@
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2530억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2531억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2688억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2693억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3004억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3021억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3371억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3415억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3655억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3735억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3802억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3942억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4099억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 4319억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1887,49 +1887,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 184874억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 185433억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 191819억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 194470억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 188633억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 195664억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 187969억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 202208억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 186298억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 210338억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 183945억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 219550억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 176262억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 224410억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 164085억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 224982억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2348,43 +2348,43 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2530억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2531억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2688억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2693억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3004억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3021억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3371억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3415억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3655억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3735억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3802억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3942억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4099억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 4319억 × 0.87% − 총차입금 28억 × 14.59% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4575,7 +4575,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 11.1, "op_wape_pct": 63.7, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 2265.3, "rev_act": 2211.32, "op_pred": 152.37, "op_act": 298.63}, {"q": "2025Q4", "rev_pred": 2533.53, "rev_act": 2318.43, "op_pred": 170.41, "op_act": 383.37}, {"q": "2026Q1", "rev_pred": 1831.63, "rev_act": 2118.22, "op_pred": 123.2, "op_act": 410.66}, {"q": "2026Q2", "rev_pred": 1982.74, "rev_act": 2433.78, "op_pred": 133.36, "op_act": 504.0}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 11.1, "op_wape_pct": 63.7, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 27.5, "wape_trend": 34.3, "adopted": true}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 2265.3, "rev_act": 2211.32, "op_pred": 152.37, "op_act": 298.63}, {"q": "2025Q4", "rev_pred": 2533.53, "rev_act": 2318.43, "op_pred": 170.41, "op_act": 383.37}, {"q": "2026Q1", "rev_pred": 1831.63, "rev_act": 2118.22, "op_pred": 123.2, "op_act": 410.66}, {"q": "2026Q2", "rev_pred": 1982.74, "rev_act": 2433.78, "op_pred": 133.36, "op_act": 504.0}]}</t>
         </is>
       </c>
     </row>
@@ -6758,29 +6758,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.303503</v>
+        <v>0.307445</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.308966</v>
+        <v>0.327057</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.167654</v>
+        <v>0.211176</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.074197</v>
+        <v>0.155571</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.007696</v>
+        <v>0.134301</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.041052</v>
+        <v>0.128966</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.065578</v>
+        <v>0.146916</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.127064</v>
+        <v>0.112622</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6907,32 +6907,32 @@
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.09507400000000001</v>
+        <v>0.095073</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.09507400000000001</v>
+        <v>0.09507500000000001</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.09507400000000001</v>
+        <v>0.09507500000000001</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.09507500000000001</v>
+        <v>0.09507599999999999</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.09507400000000001</v>
+        <v>0.09507599999999999</v>
       </c>
       <c r="AL22" s="24" t="n">
         <v>0.09507500000000001</v>
       </c>
       <c r="AM22" s="24" t="n">
+        <v>0.09507500000000001</v>
+      </c>
+      <c r="AN22" s="24" t="n">
         <v>0.09507400000000001</v>
-      </c>
-      <c r="AN22" s="24" t="n">
-        <v>0.09507599999999999</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -7062,7 +7062,7 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.137673</v>
+        <v>0.137674</v>
       </c>
       <c r="AG23" s="24" t="n">
         <v>0.137673</v>
@@ -7071,7 +7071,7 @@
         <v>0.137675</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.137675</v>
+        <v>0.137673</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
@@ -7081,13 +7081,13 @@
         <v>0.137675</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.137675</v>
+        <v>0.137674</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.137674</v>
+        <v>0.137673</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.137674</v>
+        <v>0.137673</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7339,29 +7339,29 @@
         <v>3.86</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>4.47</v>
+        <v>4.48</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>5.51</v>
+        <v>5.54</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>6.92</v>
+        <v>7.1</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>7.24</v>
+        <v>7.55</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>7.89</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7801,32 +7801,32 @@
         <v/>
       </c>
       <c r="AF28" s="24" t="n">
-        <v>0.269987</v>
+        <v>0.269985</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.269991</v>
+        <v>0.27</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.269994</v>
+        <v>0.270002</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.270012</v>
+        <v>0.269996</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ15/subQ!AJ14,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.269994</v>
+        <v>0.27001</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.269993</v>
+        <v>0.269996</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.269993</v>
+        <v>0.270001</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.269995</v>
+        <v>0.270005</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO15/subQ!AO14,"")</f>
@@ -8323,7 +8323,7 @@
         <v>165.37</v>
       </c>
       <c r="AH32" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="29" t="n">
         <v>0</v>
@@ -8451,7 +8451,7 @@
         <v>165.37</v>
       </c>
       <c r="AH33" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="29" t="n">
         <v>0</v>
@@ -8701,29 +8701,29 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.141696</v>
+        <v>0.142121</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.070007</v>
+        <v>0.071936</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.130642</v>
+        <v>0.135166</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.134121</v>
+        <v>0.143291</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.091724</v>
+        <v>0.101925</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.04338</v>
+        <v>0.059561</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.084144</v>
+        <v>0.102699</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.084188</v>
+        <v>0.108709</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8829,29 +8829,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.124653</v>
+        <v>0.125027</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.06252000000000001</v>
+        <v>0.064249</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.117492</v>
+        <v>0.121584</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.122043</v>
+        <v>0.13046</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.084357</v>
+        <v>0.093846</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.040168</v>
+        <v>0.055247</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.078155</v>
+        <v>0.095652</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.07863000000000001</v>
+        <v>0.101896</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9490,26 +9490,26 @@
         <v>-0.597441</v>
       </c>
       <c r="AG42" s="24" t="n">
-        <v>-0.570922</v>
+        <v>-0.572948</v>
       </c>
       <c r="AH42" s="24" t="n">
-        <v>-0.085202</v>
+        <v>-0.097534</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>-0.118102</v>
+        <v>-0.147903</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>-0.026895</v>
+        <v>-0.08313</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.051948</v>
+        <v>-0.137604</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.001225</v>
+        <v>-0.12795</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>0.057572</v>
+        <v>-0.117876</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -9619,16 +9619,16 @@
       </c>
       <c r="AJ43" s="25" t="n"/>
       <c r="AK43" s="24" t="n">
-        <v>-0.133333</v>
+        <v>-0.140741</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>-0.128788</v>
+        <v>-0.136364</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>-0.11811</v>
+        <v>-0.141732</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>-0.107438</v>
+        <v>-0.140496</v>
       </c>
       <c r="AO43" s="25" t="n"/>
     </row>
@@ -9910,7 +9910,7 @@
         <v/>
       </c>
       <c r="AF45" s="24" t="n">
-        <v>0.137673</v>
+        <v>0.137674</v>
       </c>
       <c r="AG45" s="24" t="n">
         <v>0.137673</v>
@@ -9919,7 +9919,7 @@
         <v>0.137675</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>0.137675</v>
+        <v>0.137673</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
@@ -9929,13 +9929,13 @@
         <v>0.137675</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>0.137675</v>
+        <v>0.137674</v>
       </c>
       <c r="AM45" s="24" t="n">
-        <v>0.137674</v>
+        <v>0.137673</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>0.137674</v>
+        <v>0.137673</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>
@@ -10430,7 +10430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO104"/>
+  <dimension ref="A1:AO114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17635,78 +17635,33 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E84" s="18" t="n">
-        <v>-530.36</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F84" s="9" t="n"/>
-      <c r="G84" s="18" t="n">
-        <v>-5034.76</v>
-      </c>
-      <c r="H84" s="18" t="n">
-        <v>-32214.02</v>
-      </c>
-      <c r="I84" s="18" t="n">
-        <v>-2962.09</v>
-      </c>
-      <c r="J84" s="18" t="n">
-        <v>32412.02</v>
-      </c>
-      <c r="K84" s="34" t="n">
-        <v>-7798.85</v>
-      </c>
-      <c r="L84" s="18" t="n">
-        <v>-27449.22</v>
-      </c>
-      <c r="M84" s="18" t="n">
-        <v>-1996.2</v>
-      </c>
-      <c r="N84" s="18" t="n">
-        <v>42214.56</v>
-      </c>
-      <c r="O84" s="18" t="n">
-        <v>43750.73</v>
-      </c>
-      <c r="P84" s="34" t="n">
-        <v>56519.87</v>
-      </c>
-      <c r="Q84" s="18" t="n">
-        <v>13586.72</v>
-      </c>
-      <c r="R84" s="18" t="n">
-        <v>72049.03</v>
-      </c>
-      <c r="S84" s="18" t="n">
-        <v>38931.98</v>
-      </c>
-      <c r="T84" s="18" t="n">
-        <v>25966.46</v>
-      </c>
-      <c r="U84" s="34" t="n">
-        <v>150534.19</v>
-      </c>
+      <c r="K84" s="9" t="n"/>
+      <c r="P84" s="9" t="n"/>
+      <c r="U84" s="9" t="n"/>
       <c r="V84" s="18" t="n">
-        <v>68777.55</v>
+        <v>1270.42</v>
       </c>
       <c r="W84" s="18" t="n">
-        <v>24604.77</v>
+        <v>1282.52</v>
       </c>
       <c r="X84" s="18" t="n">
-        <v>1794.97</v>
+        <v>1014.47</v>
       </c>
       <c r="Y84" s="18" t="n">
-        <v>36365.7</v>
+        <v>787.12</v>
       </c>
       <c r="Z84" s="34" t="n">
-        <v>131542.99</v>
+        <v>4354.53</v>
       </c>
       <c r="AA84" s="18" t="n">
-        <v>25882.55</v>
+        <v>541.73</v>
       </c>
       <c r="AB84" s="19" t="n">
-        <v>42768.85</v>
+        <v>456.22</v>
       </c>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
@@ -17728,75 +17683,30 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
-      </c>
-      <c r="E85" s="18" t="n">
-        <v>260.85</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F85" s="9" t="n"/>
-      <c r="G85" s="18" t="n">
-        <v>80.48999999999999</v>
-      </c>
-      <c r="H85" s="18" t="n">
-        <v>644.6799999999999</v>
-      </c>
-      <c r="I85" s="18" t="n">
-        <v>90.19</v>
-      </c>
-      <c r="J85" s="18" t="n">
-        <v>146.97</v>
-      </c>
-      <c r="K85" s="34" t="n">
-        <v>962.33</v>
-      </c>
-      <c r="L85" s="18" t="n">
-        <v>304.32</v>
-      </c>
-      <c r="M85" s="18" t="n">
-        <v>140.14</v>
-      </c>
-      <c r="N85" s="18" t="n">
-        <v>720.71</v>
-      </c>
-      <c r="O85" s="18" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="P85" s="34" t="n">
-        <v>1178.07</v>
-      </c>
-      <c r="Q85" s="18" t="n">
-        <v>55.84</v>
-      </c>
-      <c r="R85" s="18" t="n">
-        <v>1479.64</v>
-      </c>
-      <c r="S85" s="18" t="n">
-        <v>-1083.53</v>
-      </c>
-      <c r="T85" s="18" t="n">
-        <v>-176.43</v>
-      </c>
-      <c r="U85" s="34" t="n">
-        <v>275.52</v>
-      </c>
+      <c r="K85" s="9" t="n"/>
+      <c r="P85" s="9" t="n"/>
+      <c r="U85" s="9" t="n"/>
       <c r="V85" s="18" t="n">
-        <v>55.98</v>
+        <v>28.03</v>
       </c>
       <c r="W85" s="18" t="n">
-        <v>134.39</v>
+        <v>118.37</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>259.83</v>
+        <v>242.96</v>
       </c>
       <c r="Y85" s="18" t="n">
         <v>176.95</v>
       </c>
       <c r="Z85" s="34" t="n">
-        <v>627.15</v>
+        <v>566.3099999999999</v>
       </c>
       <c r="AA85" s="18" t="n">
-        <v>940.99</v>
+        <v>925.54</v>
       </c>
       <c r="AB85" s="19" t="n">
         <v>105.44</v>
@@ -17821,78 +17731,33 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E86" s="18" t="n">
-        <v>-301.46</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F86" s="9" t="n"/>
-      <c r="G86" s="18" t="n">
-        <v>-2960.82</v>
-      </c>
-      <c r="H86" s="18" t="n">
-        <v>-4211.69</v>
-      </c>
-      <c r="I86" s="18" t="n">
-        <v>-3071.46</v>
-      </c>
-      <c r="J86" s="18" t="n">
-        <v>-5251.16</v>
-      </c>
-      <c r="K86" s="34" t="n">
-        <v>-15495.13</v>
-      </c>
-      <c r="L86" s="18" t="n">
-        <v>-3022.94</v>
-      </c>
-      <c r="M86" s="18" t="n">
-        <v>-1257.03</v>
-      </c>
-      <c r="N86" s="18" t="n">
-        <v>-1969.93</v>
-      </c>
-      <c r="O86" s="18" t="n">
-        <v>-4375.76</v>
-      </c>
-      <c r="P86" s="34" t="n">
-        <v>-10625.66</v>
-      </c>
-      <c r="Q86" s="18" t="n">
-        <v>-786.66</v>
-      </c>
-      <c r="R86" s="18" t="n">
-        <v>854.3099999999999</v>
-      </c>
-      <c r="S86" s="18" t="n">
-        <v>172.86</v>
-      </c>
-      <c r="T86" s="18" t="n">
-        <v>-1448.94</v>
-      </c>
-      <c r="U86" s="34" t="n">
-        <v>-1208.43</v>
-      </c>
+      <c r="K86" s="9" t="n"/>
+      <c r="P86" s="9" t="n"/>
+      <c r="U86" s="9" t="n"/>
       <c r="V86" s="18" t="n">
-        <v>-5260.97</v>
+        <v>893.55</v>
       </c>
       <c r="W86" s="18" t="n">
-        <v>-4895.9</v>
+        <v>2089.03</v>
       </c>
       <c r="X86" s="18" t="n">
-        <v>-5833.57</v>
+        <v>1596.08</v>
       </c>
       <c r="Y86" s="18" t="n">
-        <v>-330.6</v>
+        <v>1513.43</v>
       </c>
       <c r="Z86" s="34" t="n">
-        <v>-16321.04</v>
+        <v>6092.09</v>
       </c>
       <c r="AA86" s="18" t="n">
-        <v>-14198.13</v>
+        <v>1859.84</v>
       </c>
       <c r="AB86" s="19" t="n">
-        <v>-17637.08</v>
+        <v>750.21</v>
       </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
@@ -17914,78 +17779,33 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>-326.98</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F87" s="9" t="n"/>
-      <c r="G87" s="18" t="n">
-        <v>9328.360000000001</v>
-      </c>
-      <c r="H87" s="18" t="n">
-        <v>-2663.32</v>
-      </c>
-      <c r="I87" s="18" t="n">
-        <v>-4977.9</v>
-      </c>
-      <c r="J87" s="18" t="n">
-        <v>-13212.11</v>
-      </c>
-      <c r="K87" s="34" t="n">
-        <v>-11524.97</v>
-      </c>
-      <c r="L87" s="18" t="n">
-        <v>-11398.89</v>
-      </c>
-      <c r="M87" s="18" t="n">
-        <v>-17625.6</v>
-      </c>
-      <c r="N87" s="18" t="n">
-        <v>4821.83</v>
-      </c>
-      <c r="O87" s="18" t="n">
-        <v>-20225.96</v>
-      </c>
-      <c r="P87" s="34" t="n">
-        <v>-44428.62</v>
-      </c>
-      <c r="Q87" s="18" t="n">
-        <v>-18871.9</v>
-      </c>
-      <c r="R87" s="18" t="n">
-        <v>-14377.61</v>
-      </c>
-      <c r="S87" s="18" t="n">
-        <v>-27945</v>
-      </c>
-      <c r="T87" s="18" t="n">
-        <v>-20412.25</v>
-      </c>
-      <c r="U87" s="34" t="n">
-        <v>-81606.75999999999</v>
-      </c>
+      <c r="K87" s="9" t="n"/>
+      <c r="P87" s="9" t="n"/>
+      <c r="U87" s="9" t="n"/>
       <c r="V87" s="18" t="n">
-        <v>-7348.66</v>
+        <v>3427.68</v>
       </c>
       <c r="W87" s="18" t="n">
-        <v>-60375.22</v>
+        <v>3023.88</v>
       </c>
       <c r="X87" s="18" t="n">
-        <v>5902.09</v>
+        <v>2493.72</v>
       </c>
       <c r="Y87" s="18" t="n">
-        <v>-126078.18</v>
+        <v>7209.12</v>
       </c>
       <c r="Z87" s="34" t="n">
-        <v>-187899.97</v>
+        <v>16154.4</v>
       </c>
       <c r="AA87" s="18" t="n">
-        <v>-28805.59</v>
+        <v>7662.48</v>
       </c>
       <c r="AB87" s="19" t="n">
-        <v>-10662.14</v>
+        <v>7573.53</v>
       </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
@@ -18007,59 +17827,33 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
-      </c>
-      <c r="E88" s="18" t="n">
-        <v>0.04</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F88" s="9" t="n"/>
-      <c r="G88" s="18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="H88" s="18" t="n">
-        <v>11.22</v>
-      </c>
-      <c r="I88" s="18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J88" s="18" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="K88" s="34" t="n">
-        <v>105.28</v>
-      </c>
-      <c r="L88" s="18" t="n">
-        <v>25.62</v>
-      </c>
-      <c r="M88" s="18" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N88" s="18" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="O88" s="18" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="P88" s="34" t="n">
-        <v>230.57</v>
-      </c>
-      <c r="S88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" s="18" t="n">
-        <v>6228.67</v>
-      </c>
+      <c r="K88" s="9" t="n"/>
+      <c r="P88" s="9" t="n"/>
       <c r="U88" s="9" t="n"/>
+      <c r="V88" s="18" t="n">
+        <v>3698.64</v>
+      </c>
+      <c r="W88" s="18" t="n">
+        <v>6173.31</v>
+      </c>
       <c r="X88" s="18" t="n">
-        <v>279.5</v>
-      </c>
-      <c r="Z88" s="9" t="n"/>
+        <v>1845</v>
+      </c>
+      <c r="Y88" s="18" t="n">
+        <v>5523.74</v>
+      </c>
+      <c r="Z88" s="34" t="n">
+        <v>17240.69</v>
+      </c>
       <c r="AA88" s="18" t="n">
-        <v>4.99</v>
+        <v>3579.48</v>
       </c>
       <c r="AB88" s="19" t="n">
-        <v>654.01</v>
+        <v>6319.09</v>
       </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
@@ -18081,59 +17875,33 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E89" s="18" t="n">
-        <v>0.04</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F89" s="9" t="n"/>
-      <c r="G89" s="18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="H89" s="18" t="n">
-        <v>11.22</v>
-      </c>
-      <c r="I89" s="18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J89" s="18" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="K89" s="34" t="n">
-        <v>105.28</v>
-      </c>
-      <c r="L89" s="18" t="n">
-        <v>25.62</v>
-      </c>
-      <c r="M89" s="18" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N89" s="18" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="O89" s="18" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="P89" s="34" t="n">
-        <v>230.57</v>
-      </c>
-      <c r="S89" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" s="18" t="n">
-        <v>6228.67</v>
-      </c>
+      <c r="K89" s="9" t="n"/>
+      <c r="P89" s="9" t="n"/>
       <c r="U89" s="9" t="n"/>
+      <c r="V89" s="18" t="n">
+        <v>845.34</v>
+      </c>
+      <c r="W89" s="18" t="n">
+        <v>-804.9</v>
+      </c>
       <c r="X89" s="18" t="n">
-        <v>279.5</v>
-      </c>
-      <c r="Z89" s="9" t="n"/>
+        <v>370.97</v>
+      </c>
+      <c r="Y89" s="18" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="Z89" s="34" t="n">
+        <v>430.99</v>
+      </c>
       <c r="AA89" s="18" t="n">
-        <v>4.99</v>
+        <v>2644.71</v>
       </c>
       <c r="AB89" s="19" t="n">
-        <v>654.01</v>
+        <v>-1258.81</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -18155,78 +17923,33 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E90" s="18" t="n">
-        <v>-781.5599999999999</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F90" s="9" t="n"/>
-      <c r="G90" s="18" t="n">
-        <v>1904.43</v>
-      </c>
-      <c r="H90" s="18" t="n">
-        <v>-6445.66</v>
-      </c>
-      <c r="I90" s="18" t="n">
-        <v>27239.18</v>
-      </c>
-      <c r="J90" s="18" t="n">
-        <v>2375.67</v>
-      </c>
-      <c r="K90" s="34" t="n">
-        <v>25073.62</v>
-      </c>
-      <c r="L90" s="18" t="n">
-        <v>11463.74</v>
-      </c>
-      <c r="M90" s="18" t="n">
-        <v>13499.35</v>
-      </c>
-      <c r="N90" s="18" t="n">
-        <v>-27169.08</v>
-      </c>
-      <c r="O90" s="18" t="n">
-        <v>-3057.9</v>
-      </c>
-      <c r="P90" s="34" t="n">
-        <v>-5263.89</v>
-      </c>
-      <c r="Q90" s="18" t="n">
-        <v>-24574.07</v>
-      </c>
-      <c r="R90" s="18" t="n">
-        <v>-13619.22</v>
-      </c>
-      <c r="S90" s="18" t="n">
-        <v>-13939.73</v>
-      </c>
-      <c r="T90" s="18" t="n">
-        <v>-29532.14</v>
-      </c>
-      <c r="U90" s="34" t="n">
-        <v>-81665.16</v>
-      </c>
+      <c r="K90" s="9" t="n"/>
+      <c r="P90" s="9" t="n"/>
+      <c r="U90" s="9" t="n"/>
       <c r="V90" s="18" t="n">
-        <v>-9148.450000000001</v>
+        <v>550.86</v>
       </c>
       <c r="W90" s="18" t="n">
-        <v>18791.52</v>
+        <v>343.49</v>
       </c>
       <c r="X90" s="18" t="n">
-        <v>-1132.35</v>
+        <v>10.95</v>
       </c>
       <c r="Y90" s="18" t="n">
-        <v>47972.09</v>
+        <v>930.51</v>
       </c>
       <c r="Z90" s="34" t="n">
-        <v>56482.81</v>
+        <v>1835.81</v>
       </c>
       <c r="AA90" s="18" t="n">
-        <v>26592.09</v>
+        <v>2223.97</v>
       </c>
       <c r="AB90" s="19" t="n">
-        <v>-2354.78</v>
+        <v>-711.33</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -18248,68 +17971,33 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
-        </is>
-      </c>
-      <c r="E91" s="18" t="n">
-        <v>335</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F91" s="9" t="n"/>
-      <c r="G91" s="18" t="n">
-        <v>296</v>
-      </c>
-      <c r="H91" s="18" t="n">
-        <v>5212</v>
-      </c>
-      <c r="I91" s="18" t="n">
-        <v>23543</v>
-      </c>
-      <c r="J91" s="18" t="n">
-        <v>14494</v>
-      </c>
-      <c r="K91" s="34" t="n">
-        <v>43545</v>
-      </c>
-      <c r="L91" s="18" t="n">
-        <v>49488.22</v>
-      </c>
-      <c r="M91" s="18" t="n">
-        <v>23388.64</v>
-      </c>
-      <c r="N91" s="18" t="n">
-        <v>27481.68</v>
-      </c>
+      <c r="K91" s="9" t="n"/>
       <c r="P91" s="9" t="n"/>
-      <c r="Q91" s="18" t="n">
-        <v>5043.5</v>
-      </c>
-      <c r="R91" s="18" t="n">
-        <v>1856.5</v>
-      </c>
-      <c r="S91" s="18" t="n">
-        <v>34414.13</v>
-      </c>
-      <c r="T91" s="18" t="n">
-        <v>18561.29</v>
-      </c>
-      <c r="U91" s="34" t="n">
-        <v>59875.42</v>
-      </c>
+      <c r="U91" s="9" t="n"/>
       <c r="V91" s="18" t="n">
-        <v>905</v>
+        <v>376.87</v>
       </c>
       <c r="W91" s="18" t="n">
-        <v>2040.82</v>
+        <v>-806.51</v>
+      </c>
+      <c r="X91" s="18" t="n">
+        <v>-581.61</v>
       </c>
       <c r="Y91" s="18" t="n">
-        <v>66109.72</v>
-      </c>
-      <c r="Z91" s="9" t="n"/>
+        <v>-726.3099999999999</v>
+      </c>
+      <c r="Z91" s="34" t="n">
+        <v>-1737.56</v>
+      </c>
       <c r="AA91" s="18" t="n">
-        <v>38870.23</v>
+        <v>-1318.11</v>
       </c>
       <c r="AB91" s="19" t="n">
-        <v>46660.48</v>
+        <v>-293.99</v>
       </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
@@ -18331,73 +18019,28 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
-        </is>
-      </c>
-      <c r="E92" s="18" t="n">
-        <v>0</v>
+          <t>파생상품이익</t>
+        </is>
       </c>
       <c r="F92" s="9" t="n"/>
-      <c r="G92" s="18" t="n">
-        <v>6105.91</v>
-      </c>
-      <c r="H92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="18" t="n">
-        <v>8205.91</v>
-      </c>
-      <c r="J92" s="18" t="n">
-        <v>214</v>
-      </c>
-      <c r="K92" s="34" t="n">
-        <v>14525.82</v>
-      </c>
-      <c r="L92" s="18" t="n">
-        <v>105.91</v>
-      </c>
-      <c r="M92" s="18" t="n">
-        <v>2700</v>
-      </c>
-      <c r="N92" s="18" t="n">
-        <v>4800</v>
-      </c>
-      <c r="O92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" s="34" t="n">
-        <v>7605.91</v>
-      </c>
-      <c r="Q92" s="18" t="n">
-        <v>4500</v>
-      </c>
-      <c r="S92" s="18" t="n">
-        <v>86.63</v>
-      </c>
-      <c r="T92" s="18" t="n">
-        <v>5446.17</v>
-      </c>
+      <c r="K92" s="9" t="n"/>
+      <c r="P92" s="9" t="n"/>
       <c r="U92" s="9" t="n"/>
-      <c r="V92" s="18" t="n">
-        <v>1235.05</v>
-      </c>
       <c r="W92" s="18" t="n">
-        <v>3764.95</v>
+        <v>4985.2</v>
       </c>
       <c r="X92" s="18" t="n">
-        <v>0</v>
+        <v>3298.69</v>
       </c>
       <c r="Y92" s="18" t="n">
-        <v>780</v>
-      </c>
-      <c r="Z92" s="34" t="n">
-        <v>5780</v>
-      </c>
+        <v>-1619.12</v>
+      </c>
+      <c r="Z92" s="9" t="n"/>
       <c r="AA92" s="18" t="n">
-        <v>1170</v>
+        <v>8887.469999999999</v>
       </c>
       <c r="AB92" s="19" t="n">
-        <v>11330</v>
+        <v>-832.85</v>
       </c>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
@@ -18419,68 +18062,28 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
-        </is>
-      </c>
-      <c r="E93" s="18" t="n">
-        <v>424</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F93" s="9" t="n"/>
-      <c r="G93" s="18" t="n">
-        <v>461</v>
-      </c>
-      <c r="H93" s="18" t="n">
-        <v>719</v>
-      </c>
-      <c r="I93" s="18" t="n">
-        <v>506</v>
-      </c>
-      <c r="J93" s="18" t="n">
-        <v>4639</v>
-      </c>
-      <c r="K93" s="34" t="n">
-        <v>6325</v>
-      </c>
-      <c r="L93" s="18" t="n">
-        <v>37677</v>
-      </c>
-      <c r="M93" s="18" t="n">
-        <v>5718</v>
-      </c>
-      <c r="N93" s="18" t="n">
-        <v>42967.43</v>
-      </c>
+      <c r="K93" s="9" t="n"/>
       <c r="P93" s="9" t="n"/>
-      <c r="Q93" s="18" t="n">
-        <v>32446.29</v>
-      </c>
-      <c r="R93" s="18" t="n">
-        <v>7204.16</v>
-      </c>
-      <c r="S93" s="18" t="n">
-        <v>36576.89</v>
-      </c>
-      <c r="T93" s="18" t="n">
-        <v>48034.16</v>
-      </c>
-      <c r="U93" s="34" t="n">
-        <v>124261.5</v>
-      </c>
-      <c r="V93" s="18" t="n">
-        <v>5456.16</v>
-      </c>
+      <c r="U93" s="9" t="n"/>
       <c r="W93" s="18" t="n">
-        <v>19180.57</v>
+        <v>12569.47</v>
+      </c>
+      <c r="X93" s="18" t="n">
+        <v>6578.81</v>
       </c>
       <c r="Y93" s="18" t="n">
-        <v>428.11</v>
+        <v>-19146.35</v>
       </c>
       <c r="Z93" s="9" t="n"/>
       <c r="AA93" s="18" t="n">
-        <v>11585</v>
+        <v>28630.13</v>
       </c>
       <c r="AB93" s="19" t="n">
-        <v>38599.44</v>
+        <v>2484.26</v>
       </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
@@ -18502,78 +18105,78 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E94" s="18" t="n">
-        <v>130.58</v>
+        <v>-530.36</v>
       </c>
       <c r="F94" s="9" t="n"/>
       <c r="G94" s="18" t="n">
-        <v>240.67</v>
+        <v>-5034.76</v>
       </c>
       <c r="H94" s="18" t="n">
-        <v>246.2</v>
+        <v>-32214.02</v>
       </c>
       <c r="I94" s="18" t="n">
-        <v>247.73</v>
+        <v>-2962.09</v>
       </c>
       <c r="J94" s="18" t="n">
-        <v>367.51</v>
+        <v>32412.02</v>
       </c>
       <c r="K94" s="34" t="n">
-        <v>1102.11</v>
+        <v>-7798.85</v>
       </c>
       <c r="L94" s="18" t="n">
-        <v>439.04</v>
+        <v>-27449.22</v>
       </c>
       <c r="M94" s="18" t="n">
-        <v>451.63</v>
+        <v>-1996.2</v>
       </c>
       <c r="N94" s="18" t="n">
-        <v>539.1900000000001</v>
+        <v>42214.56</v>
       </c>
       <c r="O94" s="18" t="n">
-        <v>510.58</v>
+        <v>43750.73</v>
       </c>
       <c r="P94" s="34" t="n">
-        <v>1940.44</v>
+        <v>56519.87</v>
       </c>
       <c r="Q94" s="18" t="n">
-        <v>529.6799999999999</v>
+        <v>13586.72</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>611.5700000000001</v>
+        <v>72049.03</v>
       </c>
       <c r="S94" s="18" t="n">
-        <v>489.8</v>
+        <v>38931.98</v>
       </c>
       <c r="T94" s="18" t="n">
-        <v>545.64</v>
+        <v>25966.46</v>
       </c>
       <c r="U94" s="34" t="n">
-        <v>2176.69</v>
+        <v>150534.19</v>
       </c>
       <c r="V94" s="18" t="n">
-        <v>548.04</v>
+        <v>68777.55</v>
       </c>
       <c r="W94" s="18" t="n">
-        <v>529.58</v>
+        <v>24604.77</v>
       </c>
       <c r="X94" s="18" t="n">
-        <v>682.01</v>
+        <v>1794.97</v>
       </c>
       <c r="Y94" s="18" t="n">
-        <v>878.96</v>
+        <v>36365.7</v>
       </c>
       <c r="Z94" s="34" t="n">
-        <v>2638.59</v>
+        <v>131542.99</v>
       </c>
       <c r="AA94" s="18" t="n">
-        <v>684.39</v>
+        <v>25882.55</v>
       </c>
       <c r="AB94" s="19" t="n">
-        <v>1231.34</v>
+        <v>42768.85</v>
       </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
@@ -18595,46 +18198,78 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>배당금지급</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E95" s="18" t="n">
-        <v>0</v>
+        <v>260.85</v>
       </c>
       <c r="F95" s="9" t="n"/>
+      <c r="G95" s="18" t="n">
+        <v>80.48999999999999</v>
+      </c>
+      <c r="H95" s="18" t="n">
+        <v>644.6799999999999</v>
+      </c>
       <c r="I95" s="18" t="n">
-        <v>0</v>
+        <v>90.19</v>
       </c>
       <c r="J95" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="9" t="n"/>
+        <v>146.97</v>
+      </c>
+      <c r="K95" s="34" t="n">
+        <v>962.33</v>
+      </c>
+      <c r="L95" s="18" t="n">
+        <v>304.32</v>
+      </c>
+      <c r="M95" s="18" t="n">
+        <v>140.14</v>
+      </c>
       <c r="N95" s="18" t="n">
-        <v>0</v>
+        <v>720.71</v>
       </c>
       <c r="O95" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" s="9" t="n"/>
+        <v>12.9</v>
+      </c>
+      <c r="P95" s="34" t="n">
+        <v>1178.07</v>
+      </c>
+      <c r="Q95" s="18" t="n">
+        <v>55.84</v>
+      </c>
+      <c r="R95" s="18" t="n">
+        <v>1479.64</v>
+      </c>
       <c r="S95" s="18" t="n">
-        <v>0</v>
+        <v>-1083.53</v>
       </c>
       <c r="T95" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U95" s="9" t="n"/>
+        <v>-176.43</v>
+      </c>
+      <c r="U95" s="34" t="n">
+        <v>275.52</v>
+      </c>
+      <c r="V95" s="18" t="n">
+        <v>55.98</v>
+      </c>
+      <c r="W95" s="18" t="n">
+        <v>134.39</v>
+      </c>
       <c r="X95" s="18" t="n">
-        <v>0</v>
+        <v>259.83</v>
       </c>
       <c r="Y95" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z95" s="9" t="n"/>
+        <v>176.95</v>
+      </c>
+      <c r="Z95" s="34" t="n">
+        <v>627.15</v>
+      </c>
       <c r="AA95" s="18" t="n">
-        <v>0</v>
+        <v>940.99</v>
       </c>
       <c r="AB95" s="19" t="n">
-        <v>16117.68</v>
+        <v>105.44</v>
       </c>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
@@ -18656,78 +18291,78 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E96" s="18" t="n">
-        <v>14.15</v>
+        <v>-301.46</v>
       </c>
       <c r="F96" s="9" t="n"/>
       <c r="G96" s="18" t="n">
-        <v>3795.81</v>
+        <v>-2960.82</v>
       </c>
       <c r="H96" s="18" t="n">
-        <v>4238.81</v>
+        <v>-4211.69</v>
       </c>
       <c r="I96" s="18" t="n">
-        <v>3795.81</v>
+        <v>-3071.46</v>
       </c>
       <c r="J96" s="18" t="n">
-        <v>4118.14</v>
+        <v>-5251.16</v>
       </c>
       <c r="K96" s="34" t="n">
-        <v>15948.57</v>
+        <v>-15495.13</v>
       </c>
       <c r="L96" s="18" t="n">
-        <v>14.15</v>
+        <v>-3022.94</v>
       </c>
       <c r="M96" s="18" t="n">
-        <v>485.44</v>
+        <v>-1257.03</v>
       </c>
       <c r="N96" s="18" t="n">
-        <v>15.75</v>
+        <v>-1969.93</v>
       </c>
       <c r="O96" s="18" t="n">
-        <v>734.37</v>
+        <v>-4375.76</v>
       </c>
       <c r="P96" s="34" t="n">
-        <v>1249.71</v>
+        <v>-10625.66</v>
       </c>
       <c r="Q96" s="18" t="n">
-        <v>941.6</v>
+        <v>-786.66</v>
       </c>
       <c r="R96" s="18" t="n">
-        <v>1530.16</v>
+        <v>854.3099999999999</v>
       </c>
       <c r="S96" s="18" t="n">
-        <v>11239.3</v>
+        <v>172.86</v>
       </c>
       <c r="T96" s="18" t="n">
-        <v>2514.3</v>
+        <v>-1448.94</v>
       </c>
       <c r="U96" s="34" t="n">
-        <v>16225.36</v>
+        <v>-1208.43</v>
       </c>
       <c r="V96" s="18" t="n">
-        <v>3284.3</v>
+        <v>-5260.97</v>
       </c>
       <c r="W96" s="18" t="n">
-        <v>784.3</v>
+        <v>-4895.9</v>
       </c>
       <c r="X96" s="18" t="n">
-        <v>784.3</v>
+        <v>-5833.57</v>
       </c>
       <c r="Y96" s="18" t="n">
-        <v>3753.05</v>
+        <v>-330.6</v>
       </c>
       <c r="Z96" s="34" t="n">
-        <v>8605.950000000001</v>
+        <v>-16321.04</v>
       </c>
       <c r="AA96" s="18" t="n">
-        <v>978.05</v>
+        <v>-14198.13</v>
       </c>
       <c r="AB96" s="19" t="n">
-        <v>2609.3</v>
+        <v>-17637.08</v>
       </c>
       <c r="AC96" s="10" t="n"/>
       <c r="AD96" s="10" t="n"/>
@@ -18749,78 +18384,78 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E97" s="18" t="n">
-        <v>-2151.43</v>
+        <v>-326.98</v>
       </c>
       <c r="F97" s="9" t="n"/>
       <c r="G97" s="18" t="n">
-        <v>6283.24</v>
+        <v>9328.360000000001</v>
       </c>
       <c r="H97" s="18" t="n">
-        <v>-41405</v>
+        <v>-2663.32</v>
       </c>
       <c r="I97" s="18" t="n">
-        <v>20029.33</v>
+        <v>-4977.9</v>
       </c>
       <c r="J97" s="18" t="n">
-        <v>19621.16</v>
+        <v>-13212.11</v>
       </c>
       <c r="K97" s="34" t="n">
-        <v>4528.73</v>
+        <v>-11524.97</v>
       </c>
       <c r="L97" s="18" t="n">
-        <v>-27419.12</v>
+        <v>-11398.89</v>
       </c>
       <c r="M97" s="18" t="n">
-        <v>-6009.93</v>
+        <v>-17625.6</v>
       </c>
       <c r="N97" s="18" t="n">
-        <v>26819.41</v>
+        <v>4821.83</v>
       </c>
       <c r="O97" s="18" t="n">
-        <v>19730.79</v>
+        <v>-20225.96</v>
       </c>
       <c r="P97" s="34" t="n">
-        <v>13121.15</v>
+        <v>-44428.62</v>
       </c>
       <c r="Q97" s="18" t="n">
-        <v>-29499.3</v>
+        <v>-18871.9</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>44662.52</v>
+        <v>-14377.61</v>
       </c>
       <c r="S97" s="18" t="n">
-        <v>-2094.22</v>
+        <v>-27945</v>
       </c>
       <c r="T97" s="18" t="n">
-        <v>-22201.85</v>
+        <v>-20412.25</v>
       </c>
       <c r="U97" s="34" t="n">
-        <v>-9132.85</v>
+        <v>-81606.75999999999</v>
       </c>
       <c r="V97" s="18" t="n">
-        <v>54217.67</v>
+        <v>-7348.66</v>
       </c>
       <c r="W97" s="18" t="n">
-        <v>-18550.06</v>
+        <v>-60375.22</v>
       </c>
       <c r="X97" s="18" t="n">
-        <v>9239.74</v>
+        <v>5902.09</v>
       </c>
       <c r="Y97" s="18" t="n">
-        <v>-44605.48</v>
+        <v>-126078.18</v>
       </c>
       <c r="Z97" s="34" t="n">
-        <v>301.87</v>
+        <v>-187899.97</v>
       </c>
       <c r="AA97" s="18" t="n">
-        <v>23543.3</v>
+        <v>-28805.59</v>
       </c>
       <c r="AB97" s="19" t="n">
-        <v>29580.97</v>
+        <v>-10662.14</v>
       </c>
       <c r="AC97" s="10" t="n"/>
       <c r="AD97" s="10" t="n"/>
@@ -18842,78 +18477,59 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>무형자산의증가</t>
         </is>
       </c>
       <c r="E98" s="18" t="n">
-        <v>-2151.43</v>
+        <v>0.04</v>
       </c>
       <c r="F98" s="9" t="n"/>
       <c r="G98" s="18" t="n">
-        <v>55331.27</v>
+        <v>1.64</v>
       </c>
       <c r="H98" s="18" t="n">
-        <v>-41405</v>
+        <v>11.22</v>
       </c>
       <c r="I98" s="18" t="n">
-        <v>20029.33</v>
+        <v>0.02</v>
       </c>
       <c r="J98" s="18" t="n">
-        <v>19621.16</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K98" s="34" t="n">
-        <v>53576.76</v>
+        <v>105.28</v>
       </c>
       <c r="L98" s="18" t="n">
-        <v>26157.63</v>
+        <v>25.62</v>
       </c>
       <c r="M98" s="18" t="n">
-        <v>-6009.93</v>
+        <v>0.15</v>
       </c>
       <c r="N98" s="18" t="n">
-        <v>26819.42</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="O98" s="18" t="n">
-        <v>19730.79</v>
+        <v>122.2</v>
       </c>
       <c r="P98" s="34" t="n">
-        <v>66697.91</v>
-      </c>
-      <c r="Q98" s="18" t="n">
-        <v>37198.61</v>
-      </c>
-      <c r="R98" s="18" t="n">
-        <v>44662.52</v>
+        <v>230.57</v>
       </c>
       <c r="S98" s="18" t="n">
-        <v>-2094.22</v>
+        <v>0</v>
       </c>
       <c r="T98" s="18" t="n">
-        <v>-22201.85</v>
-      </c>
-      <c r="U98" s="34" t="n">
-        <v>57565.06</v>
-      </c>
-      <c r="V98" s="18" t="n">
-        <v>111782.73</v>
-      </c>
-      <c r="W98" s="18" t="n">
-        <v>-18550.06</v>
-      </c>
+        <v>6228.67</v>
+      </c>
+      <c r="U98" s="9" t="n"/>
       <c r="X98" s="18" t="n">
-        <v>9239.74</v>
-      </c>
-      <c r="Y98" s="18" t="n">
-        <v>-44605.48</v>
-      </c>
-      <c r="Z98" s="34" t="n">
-        <v>57866.93</v>
-      </c>
+        <v>279.5</v>
+      </c>
+      <c r="Z98" s="9" t="n"/>
       <c r="AA98" s="18" t="n">
-        <v>81410.23</v>
+        <v>4.99</v>
       </c>
       <c r="AB98" s="19" t="n">
-        <v>29580.97</v>
+        <v>654.01</v>
       </c>
       <c r="AC98" s="10" t="n"/>
       <c r="AD98" s="10" t="n"/>
@@ -18935,45 +18551,59 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
-        </is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>0.04</v>
       </c>
       <c r="F99" s="9" t="n"/>
-      <c r="K99" s="9" t="n"/>
+      <c r="G99" s="18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H99" s="18" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="I99" s="18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J99" s="18" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="K99" s="34" t="n">
+        <v>105.28</v>
+      </c>
+      <c r="L99" s="18" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="M99" s="18" t="n">
+        <v>0.15</v>
+      </c>
       <c r="N99" s="18" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="O99" s="18" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="P99" s="34" t="n">
+        <v>230.57</v>
+      </c>
+      <c r="S99" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="O99" s="18" t="n">
-        <v>635.2</v>
-      </c>
-      <c r="P99" s="9" t="n"/>
-      <c r="S99" s="18" t="n">
-        <v>135</v>
-      </c>
       <c r="T99" s="18" t="n">
-        <v>2800</v>
+        <v>6228.67</v>
       </c>
       <c r="U99" s="9" t="n"/>
-      <c r="V99" s="18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="W99" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="X99" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y99" s="18" t="n">
-        <v>3855</v>
-      </c>
-      <c r="Z99" s="34" t="n">
-        <v>5855</v>
-      </c>
+        <v>279.5</v>
+      </c>
+      <c r="Z99" s="9" t="n"/>
       <c r="AA99" s="18" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="AB99" s="19" t="n">
-        <v>1687.5</v>
+        <v>654.01</v>
       </c>
       <c r="AC99" s="10" t="n"/>
       <c r="AD99" s="10" t="n"/>
@@ -18995,50 +18625,78 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>-781.5599999999999</v>
       </c>
       <c r="F100" s="9" t="n"/>
-      <c r="K100" s="9" t="n"/>
+      <c r="G100" s="18" t="n">
+        <v>1904.43</v>
+      </c>
+      <c r="H100" s="18" t="n">
+        <v>-6445.66</v>
+      </c>
+      <c r="I100" s="18" t="n">
+        <v>27239.18</v>
+      </c>
+      <c r="J100" s="18" t="n">
+        <v>2375.67</v>
+      </c>
+      <c r="K100" s="34" t="n">
+        <v>25073.62</v>
+      </c>
+      <c r="L100" s="18" t="n">
+        <v>11463.74</v>
+      </c>
+      <c r="M100" s="18" t="n">
+        <v>13499.35</v>
+      </c>
+      <c r="N100" s="18" t="n">
+        <v>-27169.08</v>
+      </c>
       <c r="O100" s="18" t="n">
-        <v>1653.15</v>
-      </c>
-      <c r="P100" s="9" t="n"/>
+        <v>-3057.9</v>
+      </c>
+      <c r="P100" s="34" t="n">
+        <v>-5263.89</v>
+      </c>
       <c r="Q100" s="18" t="n">
-        <v>905.77</v>
+        <v>-24574.07</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>140.92</v>
+        <v>-13619.22</v>
       </c>
       <c r="S100" s="18" t="n">
-        <v>614.15</v>
+        <v>-13939.73</v>
       </c>
       <c r="T100" s="18" t="n">
-        <v>426.33</v>
+        <v>-29532.14</v>
       </c>
       <c r="U100" s="34" t="n">
-        <v>2087.17</v>
+        <v>-81665.16</v>
       </c>
       <c r="V100" s="18" t="n">
-        <v>459.68</v>
+        <v>-9148.450000000001</v>
       </c>
       <c r="W100" s="18" t="n">
-        <v>695.6</v>
+        <v>18791.52</v>
       </c>
       <c r="X100" s="18" t="n">
-        <v>411.47</v>
+        <v>-1132.35</v>
       </c>
       <c r="Y100" s="18" t="n">
-        <v>616.6799999999999</v>
+        <v>47972.09</v>
       </c>
       <c r="Z100" s="34" t="n">
-        <v>2183.43</v>
+        <v>56482.81</v>
       </c>
       <c r="AA100" s="18" t="n">
-        <v>165.24</v>
+        <v>26592.09</v>
       </c>
       <c r="AB100" s="19" t="n">
-        <v>40.87</v>
+        <v>-2354.78</v>
       </c>
       <c r="AC100" s="10" t="n"/>
       <c r="AD100" s="10" t="n"/>
@@ -19060,18 +18718,69 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
-        </is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="n">
+        <v>335</v>
       </c>
       <c r="F101" s="9" t="n"/>
-      <c r="K101" s="9" t="n"/>
-      <c r="O101" s="18" t="n">
-        <v>8.529999999999999</v>
+      <c r="G101" s="18" t="n">
+        <v>296</v>
+      </c>
+      <c r="H101" s="18" t="n">
+        <v>5212</v>
+      </c>
+      <c r="I101" s="18" t="n">
+        <v>23543</v>
+      </c>
+      <c r="J101" s="18" t="n">
+        <v>14494</v>
+      </c>
+      <c r="K101" s="34" t="n">
+        <v>43545</v>
+      </c>
+      <c r="L101" s="18" t="n">
+        <v>49488.22</v>
+      </c>
+      <c r="M101" s="18" t="n">
+        <v>23388.64</v>
+      </c>
+      <c r="N101" s="18" t="n">
+        <v>27481.68</v>
       </c>
       <c r="P101" s="9" t="n"/>
-      <c r="U101" s="9" t="n"/>
+      <c r="Q101" s="18" t="n">
+        <v>5043.5</v>
+      </c>
+      <c r="R101" s="18" t="n">
+        <v>1856.5</v>
+      </c>
+      <c r="S101" s="18" t="n">
+        <v>34414.13</v>
+      </c>
+      <c r="T101" s="18" t="n">
+        <v>18561.29</v>
+      </c>
+      <c r="U101" s="34" t="n">
+        <v>59875.42</v>
+      </c>
+      <c r="V101" s="18" t="n">
+        <v>905</v>
+      </c>
+      <c r="W101" s="18" t="n">
+        <v>2040.82</v>
+      </c>
+      <c r="Y101" s="18" t="n">
+        <v>66109.72</v>
+      </c>
       <c r="Z101" s="9" t="n"/>
-      <c r="AB101" s="5" t="n"/>
+      <c r="AA101" s="18" t="n">
+        <v>38870.23</v>
+      </c>
+      <c r="AB101" s="19" t="n">
+        <v>46660.48</v>
+      </c>
       <c r="AC101" s="10" t="n"/>
       <c r="AD101" s="10" t="n"/>
       <c r="AE101" s="11" t="n"/>
@@ -19092,33 +18801,73 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
-        </is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="9" t="n"/>
-      <c r="K102" s="9" t="n"/>
-      <c r="P102" s="9" t="n"/>
+      <c r="G102" s="18" t="n">
+        <v>6105.91</v>
+      </c>
+      <c r="H102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="18" t="n">
+        <v>8205.91</v>
+      </c>
+      <c r="J102" s="18" t="n">
+        <v>214</v>
+      </c>
+      <c r="K102" s="34" t="n">
+        <v>14525.82</v>
+      </c>
+      <c r="L102" s="18" t="n">
+        <v>105.91</v>
+      </c>
+      <c r="M102" s="18" t="n">
+        <v>2700</v>
+      </c>
+      <c r="N102" s="18" t="n">
+        <v>4800</v>
+      </c>
+      <c r="O102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="34" t="n">
+        <v>7605.91</v>
+      </c>
+      <c r="Q102" s="18" t="n">
+        <v>4500</v>
+      </c>
+      <c r="S102" s="18" t="n">
+        <v>86.63</v>
+      </c>
+      <c r="T102" s="18" t="n">
+        <v>5446.17</v>
+      </c>
       <c r="U102" s="9" t="n"/>
       <c r="V102" s="18" t="n">
-        <v>-414.64</v>
+        <v>1235.05</v>
       </c>
       <c r="W102" s="18" t="n">
-        <v>-328.78</v>
+        <v>3764.95</v>
       </c>
       <c r="X102" s="18" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="Y102" s="18" t="n">
-        <v>277.42</v>
+        <v>780</v>
       </c>
       <c r="Z102" s="34" t="n">
-        <v>-415</v>
+        <v>5780</v>
       </c>
       <c r="AA102" s="18" t="n">
-        <v>-1000.75</v>
+        <v>1170</v>
       </c>
       <c r="AB102" s="19" t="n">
-        <v>-184.52</v>
+        <v>11330</v>
       </c>
       <c r="AC102" s="10" t="n"/>
       <c r="AD102" s="10" t="n"/>
@@ -19140,25 +18889,68 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
-        </is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>424</v>
       </c>
       <c r="F103" s="9" t="n"/>
-      <c r="K103" s="9" t="n"/>
+      <c r="G103" s="18" t="n">
+        <v>461</v>
+      </c>
+      <c r="H103" s="18" t="n">
+        <v>719</v>
+      </c>
+      <c r="I103" s="18" t="n">
+        <v>506</v>
+      </c>
+      <c r="J103" s="18" t="n">
+        <v>4639</v>
+      </c>
+      <c r="K103" s="34" t="n">
+        <v>6325</v>
+      </c>
+      <c r="L103" s="18" t="n">
+        <v>37677</v>
+      </c>
+      <c r="M103" s="18" t="n">
+        <v>5718</v>
+      </c>
+      <c r="N103" s="18" t="n">
+        <v>42967.43</v>
+      </c>
       <c r="P103" s="9" t="n"/>
-      <c r="U103" s="9" t="n"/>
-      <c r="X103" s="18" t="n">
-        <v>0</v>
+      <c r="Q103" s="18" t="n">
+        <v>32446.29</v>
+      </c>
+      <c r="R103" s="18" t="n">
+        <v>7204.16</v>
+      </c>
+      <c r="S103" s="18" t="n">
+        <v>36576.89</v>
+      </c>
+      <c r="T103" s="18" t="n">
+        <v>48034.16</v>
+      </c>
+      <c r="U103" s="34" t="n">
+        <v>124261.5</v>
+      </c>
+      <c r="V103" s="18" t="n">
+        <v>5456.16</v>
+      </c>
+      <c r="W103" s="18" t="n">
+        <v>19180.57</v>
       </c>
       <c r="Y103" s="18" t="n">
-        <v>0</v>
+        <v>428.11</v>
       </c>
       <c r="Z103" s="9" t="n"/>
       <c r="AA103" s="18" t="n">
-        <v>0</v>
+        <v>11585</v>
       </c>
       <c r="AB103" s="19" t="n">
-        <v>0</v>
+        <v>38599.44</v>
       </c>
       <c r="AC103" s="10" t="n"/>
       <c r="AD103" s="10" t="n"/>
@@ -19180,18 +18972,79 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>사채의감소</t>
-        </is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="n">
+        <v>130.58</v>
       </c>
       <c r="F104" s="9" t="n"/>
-      <c r="K104" s="9" t="n"/>
-      <c r="P104" s="9" t="n"/>
-      <c r="U104" s="9" t="n"/>
-      <c r="Z104" s="9" t="n"/>
+      <c r="G104" s="18" t="n">
+        <v>240.67</v>
+      </c>
+      <c r="H104" s="18" t="n">
+        <v>246.2</v>
+      </c>
+      <c r="I104" s="18" t="n">
+        <v>247.73</v>
+      </c>
+      <c r="J104" s="18" t="n">
+        <v>367.51</v>
+      </c>
+      <c r="K104" s="34" t="n">
+        <v>1102.11</v>
+      </c>
+      <c r="L104" s="18" t="n">
+        <v>439.04</v>
+      </c>
+      <c r="M104" s="18" t="n">
+        <v>451.63</v>
+      </c>
+      <c r="N104" s="18" t="n">
+        <v>539.1900000000001</v>
+      </c>
+      <c r="O104" s="18" t="n">
+        <v>510.58</v>
+      </c>
+      <c r="P104" s="34" t="n">
+        <v>1940.44</v>
+      </c>
+      <c r="Q104" s="18" t="n">
+        <v>529.6799999999999</v>
+      </c>
+      <c r="R104" s="18" t="n">
+        <v>611.5700000000001</v>
+      </c>
+      <c r="S104" s="18" t="n">
+        <v>489.8</v>
+      </c>
+      <c r="T104" s="18" t="n">
+        <v>545.64</v>
+      </c>
+      <c r="U104" s="34" t="n">
+        <v>2176.69</v>
+      </c>
+      <c r="V104" s="18" t="n">
+        <v>548.04</v>
+      </c>
+      <c r="W104" s="18" t="n">
+        <v>529.58</v>
+      </c>
+      <c r="X104" s="18" t="n">
+        <v>682.01</v>
+      </c>
+      <c r="Y104" s="18" t="n">
+        <v>878.96</v>
+      </c>
+      <c r="Z104" s="34" t="n">
+        <v>2638.59</v>
+      </c>
       <c r="AA104" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB104" s="5" t="n"/>
+        <v>684.39</v>
+      </c>
+      <c r="AB104" s="19" t="n">
+        <v>1231.34</v>
+      </c>
       <c r="AC104" s="10" t="n"/>
       <c r="AD104" s="10" t="n"/>
       <c r="AE104" s="11" t="n"/>
@@ -19205,6 +19058,623 @@
       <c r="AM104" s="10" t="n"/>
       <c r="AN104" s="10" t="n"/>
       <c r="AO104" s="11" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="E105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="9" t="n"/>
+      <c r="I105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="9" t="n"/>
+      <c r="N105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="9" t="n"/>
+      <c r="S105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" s="9" t="n"/>
+      <c r="X105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" s="9" t="n"/>
+      <c r="AA105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB105" s="19" t="n">
+        <v>16117.68</v>
+      </c>
+      <c r="AC105" s="10" t="n"/>
+      <c r="AD105" s="10" t="n"/>
+      <c r="AE105" s="11" t="n"/>
+      <c r="AF105" s="10" t="n"/>
+      <c r="AG105" s="10" t="n"/>
+      <c r="AH105" s="10" t="n"/>
+      <c r="AI105" s="10" t="n"/>
+      <c r="AJ105" s="11" t="n"/>
+      <c r="AK105" s="10" t="n"/>
+      <c r="AL105" s="10" t="n"/>
+      <c r="AM105" s="10" t="n"/>
+      <c r="AN105" s="10" t="n"/>
+      <c r="AO105" s="11" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>유동성장기부채의감소</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="F106" s="9" t="n"/>
+      <c r="G106" s="18" t="n">
+        <v>3795.81</v>
+      </c>
+      <c r="H106" s="18" t="n">
+        <v>4238.81</v>
+      </c>
+      <c r="I106" s="18" t="n">
+        <v>3795.81</v>
+      </c>
+      <c r="J106" s="18" t="n">
+        <v>4118.14</v>
+      </c>
+      <c r="K106" s="34" t="n">
+        <v>15948.57</v>
+      </c>
+      <c r="L106" s="18" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="M106" s="18" t="n">
+        <v>485.44</v>
+      </c>
+      <c r="N106" s="18" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="O106" s="18" t="n">
+        <v>734.37</v>
+      </c>
+      <c r="P106" s="34" t="n">
+        <v>1249.71</v>
+      </c>
+      <c r="Q106" s="18" t="n">
+        <v>941.6</v>
+      </c>
+      <c r="R106" s="18" t="n">
+        <v>1530.16</v>
+      </c>
+      <c r="S106" s="18" t="n">
+        <v>11239.3</v>
+      </c>
+      <c r="T106" s="18" t="n">
+        <v>2514.3</v>
+      </c>
+      <c r="U106" s="34" t="n">
+        <v>16225.36</v>
+      </c>
+      <c r="V106" s="18" t="n">
+        <v>3284.3</v>
+      </c>
+      <c r="W106" s="18" t="n">
+        <v>784.3</v>
+      </c>
+      <c r="X106" s="18" t="n">
+        <v>784.3</v>
+      </c>
+      <c r="Y106" s="18" t="n">
+        <v>3753.05</v>
+      </c>
+      <c r="Z106" s="34" t="n">
+        <v>8605.950000000001</v>
+      </c>
+      <c r="AA106" s="18" t="n">
+        <v>978.05</v>
+      </c>
+      <c r="AB106" s="19" t="n">
+        <v>2609.3</v>
+      </c>
+      <c r="AC106" s="10" t="n"/>
+      <c r="AD106" s="10" t="n"/>
+      <c r="AE106" s="11" t="n"/>
+      <c r="AF106" s="10" t="n"/>
+      <c r="AG106" s="10" t="n"/>
+      <c r="AH106" s="10" t="n"/>
+      <c r="AI106" s="10" t="n"/>
+      <c r="AJ106" s="11" t="n"/>
+      <c r="AK106" s="10" t="n"/>
+      <c r="AL106" s="10" t="n"/>
+      <c r="AM106" s="10" t="n"/>
+      <c r="AN106" s="10" t="n"/>
+      <c r="AO106" s="11" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E107" s="18" t="n">
+        <v>-2151.43</v>
+      </c>
+      <c r="F107" s="9" t="n"/>
+      <c r="G107" s="18" t="n">
+        <v>6283.24</v>
+      </c>
+      <c r="H107" s="18" t="n">
+        <v>-41405</v>
+      </c>
+      <c r="I107" s="18" t="n">
+        <v>20029.33</v>
+      </c>
+      <c r="J107" s="18" t="n">
+        <v>19621.16</v>
+      </c>
+      <c r="K107" s="34" t="n">
+        <v>4528.73</v>
+      </c>
+      <c r="L107" s="18" t="n">
+        <v>-27419.12</v>
+      </c>
+      <c r="M107" s="18" t="n">
+        <v>-6009.93</v>
+      </c>
+      <c r="N107" s="18" t="n">
+        <v>26819.41</v>
+      </c>
+      <c r="O107" s="18" t="n">
+        <v>19730.79</v>
+      </c>
+      <c r="P107" s="34" t="n">
+        <v>13121.15</v>
+      </c>
+      <c r="Q107" s="18" t="n">
+        <v>-29499.3</v>
+      </c>
+      <c r="R107" s="18" t="n">
+        <v>44662.52</v>
+      </c>
+      <c r="S107" s="18" t="n">
+        <v>-2094.22</v>
+      </c>
+      <c r="T107" s="18" t="n">
+        <v>-22201.85</v>
+      </c>
+      <c r="U107" s="34" t="n">
+        <v>-9132.85</v>
+      </c>
+      <c r="V107" s="18" t="n">
+        <v>54217.67</v>
+      </c>
+      <c r="W107" s="18" t="n">
+        <v>-18550.06</v>
+      </c>
+      <c r="X107" s="18" t="n">
+        <v>9239.74</v>
+      </c>
+      <c r="Y107" s="18" t="n">
+        <v>-44605.48</v>
+      </c>
+      <c r="Z107" s="34" t="n">
+        <v>301.87</v>
+      </c>
+      <c r="AA107" s="18" t="n">
+        <v>23543.3</v>
+      </c>
+      <c r="AB107" s="19" t="n">
+        <v>29580.97</v>
+      </c>
+      <c r="AC107" s="10" t="n"/>
+      <c r="AD107" s="10" t="n"/>
+      <c r="AE107" s="11" t="n"/>
+      <c r="AF107" s="10" t="n"/>
+      <c r="AG107" s="10" t="n"/>
+      <c r="AH107" s="10" t="n"/>
+      <c r="AI107" s="10" t="n"/>
+      <c r="AJ107" s="11" t="n"/>
+      <c r="AK107" s="10" t="n"/>
+      <c r="AL107" s="10" t="n"/>
+      <c r="AM107" s="10" t="n"/>
+      <c r="AN107" s="10" t="n"/>
+      <c r="AO107" s="11" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="n">
+        <v>-2151.43</v>
+      </c>
+      <c r="F108" s="9" t="n"/>
+      <c r="G108" s="18" t="n">
+        <v>55331.27</v>
+      </c>
+      <c r="H108" s="18" t="n">
+        <v>-41405</v>
+      </c>
+      <c r="I108" s="18" t="n">
+        <v>20029.33</v>
+      </c>
+      <c r="J108" s="18" t="n">
+        <v>19621.16</v>
+      </c>
+      <c r="K108" s="34" t="n">
+        <v>53576.76</v>
+      </c>
+      <c r="L108" s="18" t="n">
+        <v>26157.63</v>
+      </c>
+      <c r="M108" s="18" t="n">
+        <v>-6009.93</v>
+      </c>
+      <c r="N108" s="18" t="n">
+        <v>26819.42</v>
+      </c>
+      <c r="O108" s="18" t="n">
+        <v>19730.79</v>
+      </c>
+      <c r="P108" s="34" t="n">
+        <v>66697.91</v>
+      </c>
+      <c r="Q108" s="18" t="n">
+        <v>37198.61</v>
+      </c>
+      <c r="R108" s="18" t="n">
+        <v>44662.52</v>
+      </c>
+      <c r="S108" s="18" t="n">
+        <v>-2094.22</v>
+      </c>
+      <c r="T108" s="18" t="n">
+        <v>-22201.85</v>
+      </c>
+      <c r="U108" s="34" t="n">
+        <v>57565.06</v>
+      </c>
+      <c r="V108" s="18" t="n">
+        <v>111782.73</v>
+      </c>
+      <c r="W108" s="18" t="n">
+        <v>-18550.06</v>
+      </c>
+      <c r="X108" s="18" t="n">
+        <v>9239.74</v>
+      </c>
+      <c r="Y108" s="18" t="n">
+        <v>-44605.48</v>
+      </c>
+      <c r="Z108" s="34" t="n">
+        <v>57866.93</v>
+      </c>
+      <c r="AA108" s="18" t="n">
+        <v>81410.23</v>
+      </c>
+      <c r="AB108" s="19" t="n">
+        <v>29580.97</v>
+      </c>
+      <c r="AC108" s="10" t="n"/>
+      <c r="AD108" s="10" t="n"/>
+      <c r="AE108" s="11" t="n"/>
+      <c r="AF108" s="10" t="n"/>
+      <c r="AG108" s="10" t="n"/>
+      <c r="AH108" s="10" t="n"/>
+      <c r="AI108" s="10" t="n"/>
+      <c r="AJ108" s="11" t="n"/>
+      <c r="AK108" s="10" t="n"/>
+      <c r="AL108" s="10" t="n"/>
+      <c r="AM108" s="10" t="n"/>
+      <c r="AN108" s="10" t="n"/>
+      <c r="AO108" s="11" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>장기차입금의감소</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="n"/>
+      <c r="K109" s="9" t="n"/>
+      <c r="N109" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="18" t="n">
+        <v>635.2</v>
+      </c>
+      <c r="P109" s="9" t="n"/>
+      <c r="S109" s="18" t="n">
+        <v>135</v>
+      </c>
+      <c r="T109" s="18" t="n">
+        <v>2800</v>
+      </c>
+      <c r="U109" s="9" t="n"/>
+      <c r="V109" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W109" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="18" t="n">
+        <v>3855</v>
+      </c>
+      <c r="Z109" s="34" t="n">
+        <v>5855</v>
+      </c>
+      <c r="AA109" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="19" t="n">
+        <v>1687.5</v>
+      </c>
+      <c r="AC109" s="10" t="n"/>
+      <c r="AD109" s="10" t="n"/>
+      <c r="AE109" s="11" t="n"/>
+      <c r="AF109" s="10" t="n"/>
+      <c r="AG109" s="10" t="n"/>
+      <c r="AH109" s="10" t="n"/>
+      <c r="AI109" s="10" t="n"/>
+      <c r="AJ109" s="11" t="n"/>
+      <c r="AK109" s="10" t="n"/>
+      <c r="AL109" s="10" t="n"/>
+      <c r="AM109" s="10" t="n"/>
+      <c r="AN109" s="10" t="n"/>
+      <c r="AO109" s="11" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>이자수취(CF)</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="n"/>
+      <c r="K110" s="9" t="n"/>
+      <c r="O110" s="18" t="n">
+        <v>1653.15</v>
+      </c>
+      <c r="P110" s="9" t="n"/>
+      <c r="Q110" s="18" t="n">
+        <v>905.77</v>
+      </c>
+      <c r="R110" s="18" t="n">
+        <v>140.92</v>
+      </c>
+      <c r="S110" s="18" t="n">
+        <v>614.15</v>
+      </c>
+      <c r="T110" s="18" t="n">
+        <v>426.33</v>
+      </c>
+      <c r="U110" s="34" t="n">
+        <v>2087.17</v>
+      </c>
+      <c r="V110" s="18" t="n">
+        <v>459.68</v>
+      </c>
+      <c r="W110" s="18" t="n">
+        <v>695.6</v>
+      </c>
+      <c r="X110" s="18" t="n">
+        <v>411.47</v>
+      </c>
+      <c r="Y110" s="18" t="n">
+        <v>616.6799999999999</v>
+      </c>
+      <c r="Z110" s="34" t="n">
+        <v>2183.43</v>
+      </c>
+      <c r="AA110" s="18" t="n">
+        <v>165.24</v>
+      </c>
+      <c r="AB110" s="19" t="n">
+        <v>40.87</v>
+      </c>
+      <c r="AC110" s="10" t="n"/>
+      <c r="AD110" s="10" t="n"/>
+      <c r="AE110" s="11" t="n"/>
+      <c r="AF110" s="10" t="n"/>
+      <c r="AG110" s="10" t="n"/>
+      <c r="AH110" s="10" t="n"/>
+      <c r="AI110" s="10" t="n"/>
+      <c r="AJ110" s="11" t="n"/>
+      <c r="AK110" s="10" t="n"/>
+      <c r="AL110" s="10" t="n"/>
+      <c r="AM110" s="10" t="n"/>
+      <c r="AN110" s="10" t="n"/>
+      <c r="AO110" s="11" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>자기주식의취득</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="n"/>
+      <c r="K111" s="9" t="n"/>
+      <c r="O111" s="18" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="P111" s="9" t="n"/>
+      <c r="U111" s="9" t="n"/>
+      <c r="Z111" s="9" t="n"/>
+      <c r="AB111" s="5" t="n"/>
+      <c r="AC111" s="10" t="n"/>
+      <c r="AD111" s="10" t="n"/>
+      <c r="AE111" s="11" t="n"/>
+      <c r="AF111" s="10" t="n"/>
+      <c r="AG111" s="10" t="n"/>
+      <c r="AH111" s="10" t="n"/>
+      <c r="AI111" s="10" t="n"/>
+      <c r="AJ111" s="11" t="n"/>
+      <c r="AK111" s="10" t="n"/>
+      <c r="AL111" s="10" t="n"/>
+      <c r="AM111" s="10" t="n"/>
+      <c r="AN111" s="10" t="n"/>
+      <c r="AO111" s="11" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>이자지급(CF)</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="n"/>
+      <c r="K112" s="9" t="n"/>
+      <c r="P112" s="9" t="n"/>
+      <c r="U112" s="9" t="n"/>
+      <c r="V112" s="18" t="n">
+        <v>-414.64</v>
+      </c>
+      <c r="W112" s="18" t="n">
+        <v>-328.78</v>
+      </c>
+      <c r="X112" s="18" t="n">
+        <v>51</v>
+      </c>
+      <c r="Y112" s="18" t="n">
+        <v>277.42</v>
+      </c>
+      <c r="Z112" s="34" t="n">
+        <v>-415</v>
+      </c>
+      <c r="AA112" s="18" t="n">
+        <v>-1000.75</v>
+      </c>
+      <c r="AB112" s="19" t="n">
+        <v>-184.52</v>
+      </c>
+      <c r="AC112" s="10" t="n"/>
+      <c r="AD112" s="10" t="n"/>
+      <c r="AE112" s="11" t="n"/>
+      <c r="AF112" s="10" t="n"/>
+      <c r="AG112" s="10" t="n"/>
+      <c r="AH112" s="10" t="n"/>
+      <c r="AI112" s="10" t="n"/>
+      <c r="AJ112" s="11" t="n"/>
+      <c r="AK112" s="10" t="n"/>
+      <c r="AL112" s="10" t="n"/>
+      <c r="AM112" s="10" t="n"/>
+      <c r="AN112" s="10" t="n"/>
+      <c r="AO112" s="11" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>무형자산의감소</t>
+        </is>
+      </c>
+      <c r="F113" s="9" t="n"/>
+      <c r="K113" s="9" t="n"/>
+      <c r="P113" s="9" t="n"/>
+      <c r="U113" s="9" t="n"/>
+      <c r="X113" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y113" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" s="9" t="n"/>
+      <c r="AA113" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB113" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC113" s="10" t="n"/>
+      <c r="AD113" s="10" t="n"/>
+      <c r="AE113" s="11" t="n"/>
+      <c r="AF113" s="10" t="n"/>
+      <c r="AG113" s="10" t="n"/>
+      <c r="AH113" s="10" t="n"/>
+      <c r="AI113" s="10" t="n"/>
+      <c r="AJ113" s="11" t="n"/>
+      <c r="AK113" s="10" t="n"/>
+      <c r="AL113" s="10" t="n"/>
+      <c r="AM113" s="10" t="n"/>
+      <c r="AN113" s="10" t="n"/>
+      <c r="AO113" s="11" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>사채의감소</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="n"/>
+      <c r="K114" s="9" t="n"/>
+      <c r="P114" s="9" t="n"/>
+      <c r="U114" s="9" t="n"/>
+      <c r="Z114" s="9" t="n"/>
+      <c r="AA114" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB114" s="5" t="n"/>
+      <c r="AC114" s="10" t="n"/>
+      <c r="AD114" s="10" t="n"/>
+      <c r="AE114" s="11" t="n"/>
+      <c r="AF114" s="10" t="n"/>
+      <c r="AG114" s="10" t="n"/>
+      <c r="AH114" s="10" t="n"/>
+      <c r="AI114" s="10" t="n"/>
+      <c r="AJ114" s="11" t="n"/>
+      <c r="AK114" s="10" t="n"/>
+      <c r="AL114" s="10" t="n"/>
+      <c r="AM114" s="10" t="n"/>
+      <c r="AN114" s="10" t="n"/>
+      <c r="AO114" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19465,7 +19935,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41053,7 +41523,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2347.5</v>
+        <v>2357.7</v>
       </c>
     </row>
     <row r="30">
@@ -41073,7 +41543,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.470000000000001</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="32">
@@ -41093,7 +41563,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1801</v>
+        <v>0.1809</v>
       </c>
     </row>
     <row r="34">
@@ -41103,7 +41573,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="35">
@@ -41113,7 +41583,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>26100</v>
+        <v>26200</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/017960_model.xlsx
+++ b/argus/kship/models/017960_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 183724억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 183702억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 191578억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 191531억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 191576억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 191504억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 197453억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 197357억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 205545억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 205448억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 214748억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 214653억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 219612억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 219520억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 220188억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 220100억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 183724억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 183702억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 191578억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 191531억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 191576억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 191504억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 197453억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 197357억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 205545억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 205448억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 214748억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 214653억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 219612억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 219520억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 220188억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 220100억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2154,13 +2154,13 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3019억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3018억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3411억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3410억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2172,13 +2172,13 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3936억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3935억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4313억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4312억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2214,13 +2214,13 @@
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3019억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3018억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3411억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3410억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2232,13 +2232,13 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3936억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3935억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4313억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4312억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5652,35 +5652,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5771,35 +5771,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5890,35 +5890,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6009,35 +6009,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6128,35 +6128,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6263,7 +6263,7 @@
         <v>20100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>20650</v>
+        <v>20600</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6354,7 +6354,7 @@
         <v>27950</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>20800</v>
+        <v>21100</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6536,7 +6536,7 @@
         <v>22833.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>20400</v>
+        <v>20466.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6695,29 +6695,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.295387617</v>
+        <v>0.295231826</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.307318018</v>
+        <v>0.306997528</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.185872474</v>
+        <v>0.185428945</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.131880443</v>
+        <v>0.131333742</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.118772117</v>
+        <v>0.118374533</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.120944018</v>
+        <v>0.120722176</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.146342778</v>
+        <v>0.146292897</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.115144637</v>
+        <v>0.115239888</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7009,32 +7009,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.137675798</v>
+        <v>0.137674134</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.137673963</v>
+        <v>0.137673141</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.13767397</v>
+        <v>0.137674749</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.137674198</v>
+        <v>0.137674711</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.137673016</v>
+        <v>0.137673342</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.137674434</v>
+        <v>0.13767374</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.137675229</v>
+        <v>0.137674645</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.137673785</v>
+        <v>0.13767409</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8504,36 +8504,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.005929563</v>
+        <v>-0.005057866</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>0.002174859</v>
+        <v>0.003819853</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.001638766</v>
+        <v>-0.004414639</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>165.358815484</v>
+        <v>165.357905232</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.001300583</v>
+        <v>0.009841020000000001</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.001937498</v>
+        <v>0.001493607</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.007868818</v>
+        <v>-0.007201636</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>165.354432593</v>
+        <v>165.370142886</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.001252107</v>
+        <v>-0.005793661</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.002333475</v>
+        <v>0.010436333</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8632,36 +8632,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>-0.005929563</v>
+        <v>-0.005057866</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>0.002174859</v>
+        <v>0.003819853</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>0.001638766</v>
+        <v>-0.004414639</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>165.358815484</v>
+        <v>165.357905232</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>-0.001300583</v>
+        <v>0.009841020000000001</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.001937498</v>
+        <v>0.001493607</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.007868818</v>
+        <v>-0.007201636</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>165.354432593</v>
+        <v>165.370142886</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>0.001252107</v>
+        <v>-0.005793661</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>0.002333475</v>
+        <v>0.010436333</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8895,29 +8895,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.470414549</v>
+        <v>0.470347442</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.184467238</v>
+        <v>0.184384378</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.312922025</v>
+        <v>0.312842596</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.287657464</v>
+        <v>0.287568702</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.181569036</v>
+        <v>0.181522346</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.099442558</v>
+        <v>0.099393682</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.165606716</v>
+        <v>0.165591011</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.166449676</v>
+        <v>0.166438936</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9023,29 +9023,29 @@
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.124525369</v>
+        <v>0.124512046</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.063850878</v>
+        <v>0.06381609100000001</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.120594098</v>
+        <v>0.120554922</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.129884155</v>
+        <v>0.129831536</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.09343051600000001</v>
+        <v>0.093398312</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.055295165</v>
+        <v>0.055258175</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.09593816500000001</v>
+        <v>0.09591579</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.102556315</v>
+        <v>0.102536216</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9708,7 +9708,7 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>20650</v>
+        <v>20600</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2435638522056757</v>
+        <v>0.2435596212626919</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.09507500296054457</v>
+        <v>0.09507512370670267</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.01974058893175179</v>
+        <v>0.01974780352582841</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.0518616734701311</v>
+        <v>0.05187242352741324</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35435,7 +35435,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40824,7 +40824,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43032,7 +43032,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2358.6</v>
+        <v>2358.3</v>
       </c>
     </row>
     <row r="30">
@@ -43052,7 +43052,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.76</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/017960_model.xlsx
+++ b/argus/kship/models/017960_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 183702억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 183683억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 191531억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 191482억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 191504억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 191426억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 197357억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 197249억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 205448억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 205330억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 214653억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 214538억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 219520억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 219409억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 220100억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 219994억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 183702억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 183683억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 191531억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 191482억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 191504억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 191426억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 197357억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 197249억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 205448억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 205330억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 214653억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 214538억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 219520억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 219409억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 220100억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 219994억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2166,19 +2166,19 @@
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3729억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3728억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3935억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3934억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4312억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4311억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2226,19 +2226,19 @@
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3729억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3728억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3935억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3934억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4312억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4311억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5652,35 +5652,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5771,35 +5771,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5890,35 +5890,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6009,35 +6009,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6128,35 +6128,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6263,7 +6263,7 @@
         <v>20100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>20600</v>
+        <v>20300</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6536,7 +6536,7 @@
         <v>22833.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>20466.7</v>
+        <v>20450</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6695,29 +6695,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.295231826</v>
+        <v>0.295099639</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.306997528</v>
+        <v>0.306660603</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.185428945</v>
+        <v>0.184940312</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.131333742</v>
+        <v>0.130712355</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.118374533</v>
+        <v>0.117847118</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.120722176</v>
+        <v>0.120410551</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.146292897</v>
+        <v>0.146185103</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.115239888</v>
+        <v>0.115313787</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7009,32 +7009,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.137674134</v>
+        <v>0.137673605</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.137673141</v>
+        <v>0.13767405</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.137674749</v>
+        <v>0.137674425</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.137674711</v>
+        <v>0.13767375</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.137673342</v>
+        <v>0.137674094</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.13767374</v>
+        <v>0.13767457</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.137674645</v>
+        <v>0.137675183</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.13767409</v>
+        <v>0.137674293</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8504,36 +8504,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.005057866</v>
+        <v>-0.004414873</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>0.003819853</v>
+        <v>0.00411983</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.004414639</v>
+        <v>-0.004615361</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>165.357905232</v>
+        <v>165.364320009</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.009841020000000001</v>
+        <v>0.002860036</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.001493607</v>
+        <v>-0.009608205</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.007201636</v>
+        <v>-0.001577029</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>165.370142886</v>
+        <v>165.369565119</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.005793661</v>
+        <v>0.000282006</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.010436333</v>
+        <v>0.002677013</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8632,36 +8632,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>-0.005057866</v>
+        <v>-0.004414873</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>0.003819853</v>
+        <v>0.00411983</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.004414639</v>
+        <v>-0.004615361</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>165.357905232</v>
+        <v>165.364320009</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>0.009841020000000001</v>
+        <v>0.002860036</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>0.001493607</v>
+        <v>-0.009608205</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.007201636</v>
+        <v>-0.001577029</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>165.370142886</v>
+        <v>165.369565119</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.005793661</v>
+        <v>0.000282006</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>0.010436333</v>
+        <v>0.002677013</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8895,29 +8895,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.470347442</v>
+        <v>0.470313889</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.184384378</v>
+        <v>0.184285894</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.312842596</v>
+        <v>0.312740866</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.287568702</v>
+        <v>0.287460001</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.181522346</v>
+        <v>0.18146837</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.099393682</v>
+        <v>0.09932835399999999</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.165591011</v>
+        <v>0.165565007</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.166438936</v>
+        <v>0.166425667</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9023,29 +9023,29 @@
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.124512046</v>
+        <v>0.124498723</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.06381609100000001</v>
+        <v>0.063785252</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.120554922</v>
+        <v>0.120507871</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.129831536</v>
+        <v>0.129769399</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.093398312</v>
+        <v>0.093355465</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.055258175</v>
+        <v>0.055216995</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.09591579</v>
+        <v>0.095888217</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.102536216</v>
+        <v>0.102509922</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9708,11 +9708,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>20600</v>
+        <v>20300</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 20,300원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 20,550원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2435596212626919</v>
+        <v>0.2435605677859248</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.09507512370670267</v>
+        <v>0.09507490779402261</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.01974780352582841</v>
+        <v>0.01974285265580651</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.05187242352741324</v>
+        <v>0.05186301055542369</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35435,7 +35435,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40824,7 +40824,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43032,7 +43032,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2358.3</v>
+        <v>2358.1</v>
       </c>
     </row>
     <row r="30">
@@ -43052,7 +43052,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.74</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -43062,7 +43062,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="33">
@@ -43072,7 +43072,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.181</v>
+        <v>0.1809</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/017960_model.xlsx
+++ b/argus/kship/models/017960_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 174446억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 174137억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 183683억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 182822억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 191482억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 190578억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 191426억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 191215억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 197249억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 198979억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 205330억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 210333억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 214538억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 223494억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 219409억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 232792억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 219994억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 238047억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 174446억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 174137억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 183683억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 182822억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 191482억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 190578억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 191426억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 191215억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 197249억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 198979억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 205330억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 210333억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 214538억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 223494억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 219409억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 232792억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 219994억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 238047억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2136,49 +2136,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 2252억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 2251억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 2532억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 2530억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 2694억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 2690억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3018억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3014억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3410억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3409억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3728억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3736억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3934억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3957억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4311억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4357억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2196,49 +2196,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2252억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2251억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2532억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2530억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2694억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2690억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3018억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3014억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3410억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3409억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3728억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3736억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3934억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3957억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4311억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4357억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -6691,33 +6691,33 @@
         <v>0.203117846</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.44380033</v>
+        <v>0.441238252</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.295099639</v>
+        <v>0.289033212</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.306660603</v>
+        <v>0.300493233</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.184940312</v>
+        <v>0.183639794</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.130712355</v>
+        <v>0.142661332</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.117847118</v>
+        <v>0.150477028</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.120410551</v>
+        <v>0.172717536</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.146185103</v>
+        <v>0.217430654</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.115313787</v>
+        <v>0.196338493</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7002,39 +7002,39 @@
         <v>0.137674405</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.137673085</v>
+        <v>0.137675412</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.137673605</v>
+        <v>0.137673277</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.13767405</v>
+        <v>0.13767294</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.137674425</v>
+        <v>0.137673267</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.13767375</v>
+        <v>0.137673188</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.137674094</v>
+        <v>0.137674608</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.13767457</v>
+        <v>0.137675185</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.137675183</v>
+        <v>0.137674601</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.137674293</v>
+        <v>0.137674211</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8504,36 +8504,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.004414873</v>
+        <v>-0.00418272</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>0.00411983</v>
+        <v>0.011926408</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.004615361</v>
+        <v>-0.005410356</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>165.364320009</v>
+        <v>165.361805755</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.002860036</v>
+        <v>-0.002739145</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.009608205</v>
+        <v>-0.006266539</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.001577029</v>
+        <v>0.001329415</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>165.369565119</v>
+        <v>165.369906666</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.000282006</v>
+        <v>0.007125974</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.002677013</v>
+        <v>0.00010998</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8632,36 +8632,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>-0.004414873</v>
+        <v>-0.00418272</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>0.00411983</v>
+        <v>0.011926408</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.004615361</v>
+        <v>-0.005410356</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>165.364320009</v>
+        <v>165.361805755</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>0.002860036</v>
+        <v>-0.002739145</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.009608205</v>
+        <v>-0.006266539</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.001577029</v>
+        <v>0.001329415</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>165.369565119</v>
+        <v>165.369906666</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>0.000282006</v>
+        <v>0.007125974</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>0.002677013</v>
+        <v>0.00010998</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8891,33 +8891,33 @@
         <v>-17.576423772</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>1.345808737</v>
+        <v>1.343368752</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.470313889</v>
+        <v>0.468553195</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.184285894</v>
+        <v>0.182903539</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.312740866</v>
+        <v>0.313440772</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.287460001</v>
+        <v>0.290826654</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.18146837</v>
+        <v>0.185952228</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.09932835399999999</v>
+        <v>0.106436072</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.165565007</v>
+        <v>0.173938928</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.166425667</v>
+        <v>0.177014081</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9019,33 +9019,33 @@
         <v>0.164249189</v>
       </c>
       <c r="AD37" s="24" t="n">
-        <v>0.17906251</v>
+        <v>0.178737865</v>
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.124498723</v>
+        <v>0.123937756</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.063785252</v>
+        <v>0.063214143</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.120507871</v>
+        <v>0.120528462</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.129769399</v>
+        <v>0.131078526</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.093355465</v>
+        <v>0.09564998</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.055216995</v>
+        <v>0.059260826</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.095888217</v>
+        <v>0.101157727</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.102509922</v>
+        <v>0.109750388</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2435605677859248</v>
+        <v>0.243558221661539</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.09507490779402261</v>
+        <v>0.09507494169703327</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.01974285265580651</v>
+        <v>0.01974420991350887</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.05186301055542369</v>
+        <v>0.05186684366067711</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43032,7 +43032,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2358.1</v>
+        <v>2351.4</v>
       </c>
     </row>
     <row r="30">
@@ -43052,7 +43052,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.609999999999999</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -43072,7 +43072,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1809</v>
+        <v>0.1804</v>
       </c>
     </row>
     <row r="34">
@@ -43082,7 +43082,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -43092,7 +43092,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>26200</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/017960_model.xlsx
+++ b/argus/kship/models/017960_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 182822억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 182812억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 190578억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 190566억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 191215억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 191204억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 198979억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 198967억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 210333억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 210331억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 223494억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 223492억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 232792억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 232790억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 238047억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 238045억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 182822억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 182812억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 190578억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 190566억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 191215억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 191204억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 198979억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 198967억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 210333억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 210331억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 223494억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 223492억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 232792억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 232790억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 238047억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 238045억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2166,7 +2166,7 @@
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3736억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3735억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2226,7 +2226,7 @@
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3736억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3735억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -5295,35 +5295,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5652,35 +5652,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5771,35 +5771,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5890,35 +5890,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6009,35 +6009,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6128,35 +6128,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6263,7 +6263,7 @@
         <v>20100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>20300</v>
+        <v>19210</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6445,7 +6445,7 @@
         <v>18530</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>19960</v>
+        <v>19150</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6536,7 +6536,7 @@
         <v>22833.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>20450</v>
+        <v>20202</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6695,29 +6695,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.289033212</v>
+        <v>0.288957676</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.300493233</v>
+        <v>0.300415165</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.183639794</v>
+        <v>0.183568379</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.142661332</v>
+        <v>0.142592498</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.150477028</v>
+        <v>0.15053346</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.172717536</v>
+        <v>0.172778459</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.217430654</v>
+        <v>0.217497761</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.196338493</v>
+        <v>0.196402706</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7009,32 +7009,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.137673277</v>
+        <v>0.13767402</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.13767294</v>
+        <v>0.137674886</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.137673267</v>
+        <v>0.137675222</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.137673188</v>
+        <v>0.137673624</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.137674608</v>
+        <v>0.13767274</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.137675185</v>
+        <v>0.137673604</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.137674601</v>
+        <v>0.13767271</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.137674211</v>
+        <v>0.137672926</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8504,36 +8504,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.00418272</v>
+        <v>-0.004314116</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>0.011926408</v>
+        <v>0.0113676</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.005410356</v>
+        <v>-0.001237293</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>165.361805755</v>
+        <v>165.355535578</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.002739145</v>
+        <v>0.010774789</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.006266539</v>
+        <v>-0.010864228</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.001329415</v>
+        <v>0.001617283</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>165.369906666</v>
+        <v>165.359746331</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.007125974</v>
+        <v>-0.003269626</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.00010998</v>
+        <v>-0.010880247</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8632,36 +8632,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>-0.00418272</v>
+        <v>-0.004314116</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>0.011926408</v>
+        <v>0.0113676</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.005410356</v>
+        <v>-0.001237293</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>165.361805755</v>
+        <v>165.355535578</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>-0.002739145</v>
+        <v>0.010774789</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.006266539</v>
+        <v>-0.010864228</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>0.001329415</v>
+        <v>0.001617283</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>165.369906666</v>
+        <v>165.359746331</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>0.007125974</v>
+        <v>-0.003269626</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>0.00010998</v>
+        <v>-0.010880247</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8895,29 +8895,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.468553195</v>
+        <v>0.468519607</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.182903539</v>
+        <v>0.182884851</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.313440772</v>
+        <v>0.313443225</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.290826654</v>
+        <v>0.290815275</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.185952228</v>
+        <v>0.185960711</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.106436072</v>
+        <v>0.106440166</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.173938928</v>
+        <v>0.173940629</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.177014081</v>
+        <v>0.177016277</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9023,29 +9023,29 @@
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.123937756</v>
+        <v>0.123928871</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.063214143</v>
+        <v>0.063206738</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.120528462</v>
+        <v>0.120522819</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.131078526</v>
+        <v>0.1310745</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.09564998</v>
+        <v>0.09565222499999999</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.059260826</v>
+        <v>0.059262095</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.101157727</v>
+        <v>0.101157245</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.109750388</v>
+        <v>0.10975036</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9708,11 +9708,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>20300</v>
+        <v>19210</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 20,550원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 20,500원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.243558221661539</v>
+        <v>0.2435602013362341</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.09507494169703327</v>
+        <v>0.09507416985190649</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.01974420991350887</v>
+        <v>0.01973951551033675</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.05186684366067711</v>
+        <v>0.05185924883416584</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40824,7 +40824,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43052,7 +43052,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.630000000000001</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="32">
@@ -43062,7 +43062,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/017960_model.xlsx
+++ b/argus/kship/models/017960_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 174137억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 174980억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 182812억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 185290억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 190566억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 193745억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 191204억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 194363억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 198967억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 200740억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 210331억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 209575억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 223492억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 220928억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 232790억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 229100억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 238045억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 233908억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 174137억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 174980억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 182812억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 185290억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 190566억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 193745억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 191204억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 194363억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 198967억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 200740억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 210331억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 209575억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 223492억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 220928억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 232790억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 229100억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 238045억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 233908억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2136,49 +2136,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 2251억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 2253억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 2530억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 2536억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 2690억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 2701억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3014억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3031억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3409억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3429억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3735억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3754억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3957억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3971억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4357억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4365억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2196,49 +2196,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2251억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2253억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2530억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2536억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2690억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2701억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3014억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3031억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3409억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3429억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3735억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3754억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3957억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3971억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4357억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4365억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4625,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 기타금융손익(금융손익 − 이자 − 외환 − 파생 잔차) 최근 4분기 중위 -40.7억이 이자손익 추정 -10.2억의 50% 초과 → 추정 0 — 평가손익·재분류 여부는 주석 확인 / 금융손익 실적→추정 단절: 최근 4분기 실적 -83/+16/-193/-31(중위 -57억) → 추정 2026Q3 -10억(차 +46억, +82%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 이자발생자산 이자율: 주석 연율 2.0% 가 CF 연율 0.9% 의 2.3배 — 최근 4분기 연속 주석이라 유지(차입금 외 이자 포함 가능 — 주석 확인). 클립 조건: stale 또는 &gt; 20% / 총차입금 이자율: 주석 연율 5.2% 가 CF 연율 1.4% 의 3.8배 — 최근 4분기 연속 주석이라 유지(차입금 외 이자 포함 가능 — 주석 확인). 클립 조건: stale 또는 &gt; 20% / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 기타금융손익(금융손익 − 이자 − 외환 − 파생 잔차) 최근 4분기 중위 -40.7억이 이자손익 추정 -10.2억의 50% 초과 → 추정 0 — 평가손익·재분류 여부는 주석 확인 / 금융손익 실적→추정 단절: 최근 4분기 실적 -83/+16/-193/-31(중위 -57억) → 추정 2026Q3 -10억(차 +46억, +82%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -6691,33 +6691,33 @@
         <v>0.203117846</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.441238252</v>
+        <v>0.448221426</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.288957676</v>
+        <v>0.306434652</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.300415165</v>
+        <v>0.322109844</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.183568379</v>
+        <v>0.203121241</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.142592498</v>
+        <v>0.147212294</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.15053346</v>
+        <v>0.131062295</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.172778459</v>
+        <v>0.140298099</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.217497761</v>
+        <v>0.17872585</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.196402706</v>
+        <v>0.165231004</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7002,39 +7002,39 @@
         <v>0.137674405</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.137675412</v>
+        <v>0.137672742</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.13767402</v>
+        <v>0.137675215</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.137674886</v>
+        <v>0.137675124</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.137675222</v>
+        <v>0.137674639</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.137673624</v>
+        <v>0.137673032</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.13767274</v>
+        <v>0.137674121</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.137673604</v>
+        <v>0.137674563</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.13767271</v>
+        <v>0.137674399</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.137672926</v>
+        <v>0.137674814</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8504,36 +8504,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.004314116</v>
+        <v>-0.005473266</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>0.0113676</v>
+        <v>-0.000134193</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.001237293</v>
+        <v>0.002631146</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>165.355535578</v>
+        <v>165.365677834</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.010774789</v>
+        <v>-0.001448033</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.010864228</v>
+        <v>0.001774061</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.001617283</v>
+        <v>-0.004326915</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>165.359746331</v>
+        <v>165.369889432</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.003269626</v>
+        <v>-0.00022978</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.010880247</v>
+        <v>0.002804175</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8632,36 +8632,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>-0.004314116</v>
+        <v>-0.005473266</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>0.0113676</v>
+        <v>-0.000134193</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.001237293</v>
+        <v>0.002631146</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>165.355535578</v>
+        <v>165.365677834</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>0.010774789</v>
+        <v>-0.001448033</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.010864228</v>
+        <v>0.001774061</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>0.001617283</v>
+        <v>-0.004326915</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>165.359746331</v>
+        <v>165.369889432</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.003269626</v>
+        <v>-0.00022978</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.010880247</v>
+        <v>0.002804175</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8891,33 +8891,33 @@
         <v>-17.576423772</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>1.343368752</v>
+        <v>1.350019677</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.468519607</v>
+        <v>0.473657769</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.182884851</v>
+        <v>0.188004273</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.313443225</v>
+        <v>0.315337376</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.290815275</v>
+        <v>0.289946767</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.185960711</v>
+        <v>0.183224526</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.106440166</v>
+        <v>0.103398165</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.173940629</v>
+        <v>0.170132007</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.177016277</v>
+        <v>0.173431053</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9019,33 +9019,33 @@
         <v>0.164249189</v>
       </c>
       <c r="AD37" s="24" t="n">
-        <v>0.178737865</v>
+        <v>0.179622784</v>
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.123928871</v>
+        <v>0.125549312</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.063206738</v>
+        <v>0.06524534</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.120522819</v>
+        <v>0.122050276</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.1310745</v>
+        <v>0.131547429</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.09565222499999999</v>
+        <v>0.094770022</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.059262095</v>
+        <v>0.057797772</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.101157245</v>
+        <v>0.09920508</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.10975036</v>
+        <v>0.107654176</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2435602013362341</v>
+        <v>0.2435604776595881</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.09507416985190649</v>
+        <v>0.09507414633231251</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.01973951551033675</v>
+        <v>0.01974712637608305</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.05185924883416584</v>
+        <v>0.05187205055792288</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43032,7 +43032,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2351.4</v>
+        <v>2372.6</v>
       </c>
     </row>
     <row r="30">
@@ -43052,7 +43052,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.17</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="32">
@@ -43072,7 +43072,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1804</v>
+        <v>0.1821</v>
       </c>
     </row>
     <row r="34">
@@ -43082,7 +43082,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="35">
@@ -43092,7 +43092,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>26100</v>
+        <v>26300</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/017960_model.xlsx
+++ b/argus/kship/models/017960_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 185290억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 185287억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 193745억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 193771억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 194363억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 194418억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 200740억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 200823억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 209575억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 209689억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 220928억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 221039억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 229100억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 229208억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 233908억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 234011억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 185290억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 185287억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 193745억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 193771억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 194363억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 194418억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 200740억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 200823억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 209575억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 209689억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 220928억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 221039억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 229100억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 229208억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 233908억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 234011억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2160,25 +2160,25 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3429억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3430억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3754억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3755억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3971억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3972억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4365억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4366억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2220,25 +2220,25 @@
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3429억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3430억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3754억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3755억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3971억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3972억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4365억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4366억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -5295,35 +5295,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5652,35 +5652,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5771,35 +5771,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5890,35 +5890,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6009,35 +6009,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6128,35 +6128,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6263,7 +6263,7 @@
         <v>20100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>19210</v>
+        <v>19260</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6536,7 +6536,7 @@
         <v>22833.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>20202</v>
+        <v>20212</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6695,29 +6695,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.306434652</v>
+        <v>0.306411048</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.322109844</v>
+        <v>0.322286524</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.203121241</v>
+        <v>0.203463285</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.147212294</v>
+        <v>0.147688825</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.131062295</v>
+        <v>0.131697058</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.140298099</v>
+        <v>0.1407206</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.17872585</v>
+        <v>0.178943653</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.165231004</v>
+        <v>0.165261011</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7009,32 +7009,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.137675215</v>
+        <v>0.137674089</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.137675124</v>
+        <v>0.137675372</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.137674639</v>
+        <v>0.137672989</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.137673032</v>
+        <v>0.137672961</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.137674121</v>
+        <v>0.137672829</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.137674563</v>
+        <v>0.137673283</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.137674399</v>
+        <v>0.137673423</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.137674814</v>
+        <v>0.137674236</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8504,36 +8504,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.005473266</v>
+        <v>-0.006426595</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.000134193</v>
+        <v>-0.001167437</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.002631146</v>
+        <v>-0.005780712</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>165.365677834</v>
+        <v>165.370148428</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.001448033</v>
+        <v>-0.001364947</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.001774061</v>
+        <v>-0.012219813</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.004326915</v>
+        <v>9.8556e-05</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>165.369889432</v>
+        <v>165.360077122</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.00022978</v>
+        <v>0.003165581</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.002804175</v>
+        <v>-0.000491983</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8632,36 +8632,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>-0.005473266</v>
+        <v>-0.006426595</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.000134193</v>
+        <v>-0.001167437</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>0.002631146</v>
+        <v>-0.005780712</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>165.365677834</v>
+        <v>165.370148428</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>-0.001448033</v>
+        <v>-0.001364947</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>0.001774061</v>
+        <v>-0.012219813</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.004326915</v>
+        <v>9.8556e-05</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>165.369889432</v>
+        <v>165.360077122</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.00022978</v>
+        <v>0.003165581</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>0.002804175</v>
+        <v>-0.000491983</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8895,29 +8895,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.473657769</v>
+        <v>0.473641022</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.188004273</v>
+        <v>0.188063229</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.315337376</v>
+        <v>0.315420963</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.289946767</v>
+        <v>0.290033595</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.183224526</v>
+        <v>0.18330064</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.103398165</v>
+        <v>0.103459774</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.170132007</v>
+        <v>0.17016482</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.173431053</v>
+        <v>0.173453502</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9023,29 +9023,29 @@
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.125549312</v>
+        <v>0.125544873</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.06524534</v>
+        <v>0.065265317</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.122050276</v>
+        <v>0.122081788</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.131547429</v>
+        <v>0.131597875</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.094770022</v>
+        <v>0.09481421399999999</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.057797772</v>
+        <v>0.057843646</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.09920508</v>
+        <v>0.09923341300000001</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.107654176</v>
+        <v>0.107681068</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9708,11 +9708,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>19210</v>
+        <v>19260</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 20,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 20,250원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2435604776595881</v>
+        <v>0.2435618888700624</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.09507414633231251</v>
+        <v>0.09507506041490912</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.01974712637608305</v>
+        <v>0.01974825289442047</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.05187205055792288</v>
+        <v>0.05187504417307687</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2372.6</v>
+        <v>2372.7</v>
       </c>
     </row>
     <row r="30">
@@ -43052,7 +43052,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.1</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -43062,7 +43062,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/017960_model.xlsx
+++ b/argus/kship/models/017960_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 185287억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 185284억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 193771억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 193756억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 194418억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 194390억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 200823억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 200784억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 209689억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 209642억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 221039억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 220993억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 229208억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 229163억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 234011억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 233969억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 185287억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 185284억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 193771억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 193756억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 194418억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 194390억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 200823억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 200784억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 209689억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 209642억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 221039억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 220993억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 229208억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 229163억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 234011억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 233969억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5652,35 +5652,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5771,35 +5771,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5890,35 +5890,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6009,35 +6009,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6128,35 +6128,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6695,29 +6695,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.306411048</v>
+        <v>0.306387443</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.322286524</v>
+        <v>0.322179694</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.203463285</v>
+        <v>0.203290384</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.147688825</v>
+        <v>0.147462473</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.131697058</v>
+        <v>0.131464544</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.1407206</v>
+        <v>0.140576589</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.178943653</v>
+        <v>0.178885026</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.165261011</v>
+        <v>0.165278037</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7009,32 +7009,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.137674089</v>
+        <v>0.137672963</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.137675372</v>
+        <v>0.137674066</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.137672989</v>
+        <v>0.137674029</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.137672961</v>
+        <v>0.137674163</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.137672829</v>
+        <v>0.137674864</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.137673283</v>
+        <v>0.137674545</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.137673423</v>
+        <v>0.137673556</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.137674236</v>
+        <v>0.137674881</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8504,36 +8504,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.006426595</v>
+        <v>-0.004330132</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.001167437</v>
+        <v>0.001043259</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.005780712</v>
+        <v>-0.001711291</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>165.370148428</v>
+        <v>165.36150829</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.001364947</v>
+        <v>0.004605395</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.012219813</v>
+        <v>-0.006652731</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>9.8556e-05</v>
+        <v>0.002243721</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>165.360077122</v>
+        <v>165.364349152</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.003165581</v>
+        <v>0.007007229</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.000491983</v>
+        <v>-0.004456199</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8632,36 +8632,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>-0.006426595</v>
+        <v>-0.004330132</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.001167437</v>
+        <v>0.001043259</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.005780712</v>
+        <v>-0.001711291</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>165.370148428</v>
+        <v>165.36150829</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>-0.001364947</v>
+        <v>0.004605395</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.012219813</v>
+        <v>-0.006652731</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>9.8556e-05</v>
+        <v>0.002243721</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>165.360077122</v>
+        <v>165.364349152</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>0.003165581</v>
+        <v>0.007007229</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.000491983</v>
+        <v>-0.004456199</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8898,26 +8898,26 @@
         <v>0.473641022</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.188063229</v>
+        <v>0.188017773</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.315420963</v>
+        <v>0.31539477</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.290033595</v>
+        <v>0.289992292</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.18330064</v>
+        <v>0.183272075</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.103459774</v>
+        <v>0.103438255</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.17016482</v>
+        <v>0.170153056</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.173453502</v>
+        <v>0.173445254</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9026,26 +9026,26 @@
         <v>0.125544873</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.065265317</v>
+        <v>0.065253485</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.122081788</v>
+        <v>0.122064633</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.131597875</v>
+        <v>0.131574953</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.09481421399999999</v>
+        <v>0.09479531099999999</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.057843646</v>
+        <v>0.057826037</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.09923341300000001</v>
+        <v>0.099223783</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.107681068</v>
+        <v>0.107670073</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2435618888700624</v>
+        <v>0.2435583374804798</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.09507506041490912</v>
+        <v>0.09507481543416162</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.01974825289442047</v>
+        <v>0.01974371293044709</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.05187504417307687</v>
+        <v>0.05186666404455141</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/017960_model.xlsx
+++ b/argus/kship/models/017960_model.xlsx
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/017960_model.xlsx
+++ b/argus/kship/models/017960_model.xlsx
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
         <v>20100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>19260</v>
+        <v>18590</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6445,7 +6445,7 @@
         <v>18530</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>19150</v>
+        <v>18550</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6536,7 +6536,7 @@
         <v>22833.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>20212</v>
+        <v>19941.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9708,7 +9708,7 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>19260</v>
+        <v>18590</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35435,7 +35435,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40824,7 +40824,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43052,7 +43052,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.119999999999999</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="32">
@@ -43062,7 +43062,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/017960_model.xlsx
+++ b/argus/kship/models/017960_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 185284억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 185274억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 193756억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 193695억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 194390억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 194278억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 200784억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 200619억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 209642억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 209436억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 220993억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 220789억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 229163억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 228965억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 233969억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 233778억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 185284억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 185274억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 193756억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 193695억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 194390억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 194278억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 200784억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 200619억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 209642억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 209436억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 220993억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 220789억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 229163억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 228965억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 233969억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 233778억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2160,25 +2160,25 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3430억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3429억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3755억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3754억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3972억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3971억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4366억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4364억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2220,25 +2220,25 @@
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3430억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3429억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3755억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3754억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3972억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3971억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4366억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4364억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5652,35 +5652,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5771,35 +5771,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5890,35 +5890,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6009,35 +6009,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6128,35 +6128,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6263,7 +6263,7 @@
         <v>20100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18590</v>
+        <v>18400</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6445,7 +6445,7 @@
         <v>18530</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>18550</v>
+        <v>17670</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6536,7 +6536,7 @@
         <v>22833.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19941.7</v>
+        <v>19715.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6695,29 +6695,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.306387443</v>
+        <v>0.306316629</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.322179694</v>
+        <v>0.321764701</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.203290384</v>
+        <v>0.20259502</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.147462473</v>
+        <v>0.146524303</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.131464544</v>
+        <v>0.130412785</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.140576589</v>
+        <v>0.139883987</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.178885026</v>
+        <v>0.178544639</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.165278037</v>
+        <v>0.165283395</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7009,32 +7009,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.137672963</v>
+        <v>0.137673198</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.137674066</v>
+        <v>0.137673771</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.137674029</v>
+        <v>0.137675497</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.137674163</v>
+        <v>0.137675117</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.137674864</v>
+        <v>0.137672958</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.137674545</v>
+        <v>0.137673274</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.137673556</v>
+        <v>0.137673607</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.137674881</v>
+        <v>0.137673212</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8504,36 +8504,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.004330132</v>
+        <v>-0.006381793</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>0.001043259</v>
+        <v>-0.001333589</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.001711291</v>
+        <v>-0.008649682000000001</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>165.36150829</v>
+        <v>165.363568693</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.004605395</v>
+        <v>0.00314219</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.006652731</v>
+        <v>0.004788751</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.002243721</v>
+        <v>-0.006863115</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>165.364349152</v>
+        <v>165.363597802</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.007007229</v>
+        <v>-0.009917373</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.004456199</v>
+        <v>0.001652558</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8632,36 +8632,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>-0.004330132</v>
+        <v>-0.006381793</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>0.001043259</v>
+        <v>-0.001333589</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.001711291</v>
+        <v>-0.008649682000000001</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>165.36150829</v>
+        <v>165.363568693</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>0.004605395</v>
+        <v>0.00314219</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.006652731</v>
+        <v>0.004788751</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>0.002243721</v>
+        <v>-0.006863115</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>165.364349152</v>
+        <v>165.363597802</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>0.007007229</v>
+        <v>-0.009917373</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.004456199</v>
+        <v>0.001652558</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8895,29 +8895,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.473641022</v>
+        <v>0.473607529</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.188017773</v>
+        <v>0.187908404</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.31539477</v>
+        <v>0.315239644</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.289992292</v>
+        <v>0.289827032</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.183272075</v>
+        <v>0.183157764</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.103438255</v>
+        <v>0.103313998</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.170153056</v>
+        <v>0.170098884</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.173445254</v>
+        <v>0.173411898</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9023,29 +9023,29 @@
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.125544873</v>
+        <v>0.125535995</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.065253485</v>
+        <v>0.065210618</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.122064633</v>
+        <v>0.122003865</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.131574953</v>
+        <v>0.13147952</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.09479531099999999</v>
+        <v>0.094719682</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.057826037</v>
+        <v>0.057744922</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.099223783</v>
+        <v>0.099168621</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.107670073</v>
+        <v>0.107624202</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9708,11 +9708,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>18590</v>
+        <v>18400</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 20,250원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,150원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2435583374804798</v>
+        <v>0.2435631621422071</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.09507481543416162</v>
+        <v>0.09507474980521917</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.01974371293044709</v>
+        <v>0.01974654407417072</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.05186666404455141</v>
+        <v>0.05187119653541379</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35435,7 +35435,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40824,7 +40824,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43032,7 +43032,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2372.7</v>
+        <v>2372.5</v>
       </c>
     </row>
     <row r="30">
@@ -43052,7 +43052,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.83</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="32">
@@ -43062,7 +43062,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="33">
@@ -43072,7 +43072,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1821</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/017960_model.xlsx
+++ b/argus/kship/models/017960_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 185274억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 185272억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 193695억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 193744억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 194278억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 194378억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 200619억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 200769억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 209436억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 209636억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 220789억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 220984억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 228965억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 229153억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 233778억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 233959억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 185274억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 185272억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 193695억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 193744억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 194278억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 194378억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 200619억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 200769억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 209436억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 209636억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 220789억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 220984억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 228965억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 229153억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 233778억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 233959억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2160,25 +2160,25 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3429억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3430억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3754억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3755억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3971억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3972억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4364억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4366억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2220,25 +2220,25 @@
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3429억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3430억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3754억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3755억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3971억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3972억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4364억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4366억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5652,35 +5652,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5771,35 +5771,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5890,35 +5890,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6009,35 +6009,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6128,35 +6128,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6263,7 +6263,7 @@
         <v>20100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18400</v>
+        <v>18790</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6536,7 +6536,7 @@
         <v>22833.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19715.7</v>
+        <v>19607.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6695,29 +6695,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.306316629</v>
+        <v>0.306307187</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.321764701</v>
+        <v>0.322101626</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.20259502</v>
+        <v>0.203215209</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.146524303</v>
+        <v>0.147376102</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.130412785</v>
+        <v>0.131501532</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.139883987</v>
+        <v>0.140600429</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.178544639</v>
+        <v>0.178905574</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.165283395</v>
+        <v>0.165316437</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7009,32 +7009,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.137673198</v>
+        <v>0.137674193</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.137673771</v>
+        <v>0.137672872</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.137675497</v>
+        <v>0.137673259</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.137675117</v>
+        <v>0.137674143</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.137672958</v>
+        <v>0.137672434</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.137673274</v>
+        <v>0.137674348</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.137673607</v>
+        <v>0.137674458</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.137673212</v>
+        <v>0.137674025</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8504,36 +8504,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.006381793</v>
+        <v>-0.004682195</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.001333589</v>
+        <v>0.000664202</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.008649682000000001</v>
+        <v>0.002913432</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>165.363568693</v>
+        <v>165.358498113</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.00314219</v>
+        <v>0.001554486</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.004788751</v>
+        <v>-0.007354829</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.006863115</v>
+        <v>-0.003280034</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>165.363597802</v>
+        <v>165.368828282</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.009917373</v>
+        <v>0.00143932</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.001652558</v>
+        <v>0.002331981</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8632,36 +8632,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>-0.006381793</v>
+        <v>-0.004682195</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.001333589</v>
+        <v>0.000664202</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.008649682000000001</v>
+        <v>0.002913432</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>165.363568693</v>
+        <v>165.358498113</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>0.00314219</v>
+        <v>0.001554486</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>0.004788751</v>
+        <v>-0.007354829</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.006863115</v>
+        <v>-0.003280034</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>165.363597802</v>
+        <v>165.368828282</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.009917373</v>
+        <v>0.00143932</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>0.001652558</v>
+        <v>0.002331981</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8898,26 +8898,26 @@
         <v>0.473607529</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.187908404</v>
+        <v>0.188010682</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.315239644</v>
+        <v>0.315375123</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.289827032</v>
+        <v>0.289983128</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.183157764</v>
+        <v>0.183275737</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.103313998</v>
+        <v>0.103438419</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.170098884</v>
+        <v>0.170152502</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.173411898</v>
+        <v>0.173446194</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9026,26 +9026,26 @@
         <v>0.125535995</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.065210618</v>
+        <v>0.065246112</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.122003865</v>
+        <v>0.122059036</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.13147952</v>
+        <v>0.13156766</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.094719682</v>
+        <v>0.094797799</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.057744922</v>
+        <v>0.057822097</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.099168621</v>
+        <v>0.09922149600000001</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.107624202</v>
+        <v>0.107668698</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9708,11 +9708,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>18400</v>
+        <v>18790</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,150원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,610원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2435631621422071</v>
+        <v>0.243559161328797</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.09507474980521917</v>
+        <v>0.09507472480644351</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.01974654407417072</v>
+        <v>0.0197447563834671</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.05187119653541379</v>
+        <v>0.05186809440765527</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35435,7 +35435,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40824,7 +40824,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43032,7 +43032,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2372.5</v>
+        <v>2372.6</v>
       </c>
     </row>
     <row r="30">
@@ -43052,7 +43052,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.76</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="32">
@@ -43062,7 +43062,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="33">
@@ -43072,7 +43072,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.182</v>
+        <v>0.1821</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/017960_model.xlsx
+++ b/argus/kship/models/017960_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 185272억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 185386억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 193744억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 193895억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 194378억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 194492억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 200769억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 200790억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 209636억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 209407억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 220984억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 220555억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 229153억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 228588억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 233959억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 233324억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 185272억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 185386억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 193744억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 193895억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 194378억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 194492억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 200769억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 200790억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 209636억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 209407억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 220984억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 220555억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 229153억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 228588억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 233959억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 233324억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2148,7 +2148,7 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 2701억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 2702억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2172,13 +2172,13 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3972억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3971억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4366억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 4364억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2208,7 +2208,7 @@
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2701억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2702억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2232,13 +2232,13 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3972억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3971억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 4366억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 4364억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 1.97% / 부채 5.19% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0197, 0.0519] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
+          <t>· 이자율 자산 1.98% / 부채 5.19% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0197, 0.0519] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5652,35 +5652,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5771,35 +5771,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5890,35 +5890,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6009,35 +6009,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6128,35 +6128,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6263,7 +6263,7 @@
         <v>20100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18790</v>
+        <v>18190</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6445,7 +6445,7 @@
         <v>18530</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>17670</v>
+        <v>17220</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6536,7 +6536,7 @@
         <v>22833.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19607.5</v>
+        <v>19117.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6695,29 +6695,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.306307187</v>
+        <v>0.307105028</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.322101626</v>
+        <v>0.323132945</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.203215209</v>
+        <v>0.203925607</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.147376102</v>
+        <v>0.147498213</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.131501532</v>
+        <v>0.129575654</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.140600429</v>
+        <v>0.137494139</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.178905574</v>
+        <v>0.17530643</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.165316437</v>
+        <v>0.162031125</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7009,32 +7009,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.137674193</v>
+        <v>0.137673229</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.137672872</v>
+        <v>0.137674251</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.137673259</v>
+        <v>0.137673196</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.137674143</v>
+        <v>0.137675066</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.137672434</v>
+        <v>0.137672702</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.137674348</v>
+        <v>0.137675165</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.137674458</v>
+        <v>0.137674557</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.137674025</v>
+        <v>0.137673326</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8504,36 +8504,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.004682195</v>
+        <v>-0.006100722</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>0.000664202</v>
+        <v>-0.000547042</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.002913432</v>
+        <v>-0.003626296</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>165.358498113</v>
+        <v>165.363701638</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.001554486</v>
+        <v>-9.3891e-05</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.007354829</v>
+        <v>0.000769446</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.003280034</v>
+        <v>-0.005071874</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>165.368828282</v>
+        <v>165.370207399</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.00143932</v>
+        <v>0.003423587</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.002331981</v>
+        <v>-0.001491496</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8632,36 +8632,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>-0.004682195</v>
+        <v>-0.006100722</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>0.000664202</v>
+        <v>-0.000547042</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>0.002913432</v>
+        <v>-0.003626296</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>165.358498113</v>
+        <v>165.363701638</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>0.001554486</v>
+        <v>-9.3891e-05</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.007354829</v>
+        <v>0.000769446</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.003280034</v>
+        <v>-0.005071874</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>165.368828282</v>
+        <v>165.370207399</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>0.00143932</v>
+        <v>0.003423587</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>0.002331981</v>
+        <v>-0.001491496</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8895,29 +8895,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.473607529</v>
+        <v>0.47389222</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.188010682</v>
+        <v>0.188269781</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.315375123</v>
+        <v>0.315446253</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.289983128</v>
+        <v>0.289877301</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.183275737</v>
+        <v>0.183008267</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.103438419</v>
+        <v>0.10306489</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.170152502</v>
+        <v>0.169764469</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.173446194</v>
+        <v>0.173066345</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9023,29 +9023,29 @@
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.125535995</v>
+        <v>0.125615895</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.065246112</v>
+        <v>0.06534401200000001</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.122059036</v>
+        <v>0.122113189</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.13156766</v>
+        <v>0.131556377</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.094797799</v>
+        <v>0.09467086500000001</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.057822097</v>
+        <v>0.057620095</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.09922149600000001</v>
+        <v>0.09898773700000001</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.107668698</v>
+        <v>0.107411998</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9708,11 +9708,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>18790</v>
+        <v>18190</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,610원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 17,550원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.243559161328797</v>
+        <v>0.243561257414456</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.09507472480644351</v>
+        <v>0.09507496555945608</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.0197447563834671</v>
+        <v>0.01975282745898116</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.05186809440765527</v>
+        <v>0.05187997566164976</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35435,7 +35435,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40824,7 +40824,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43032,7 +43032,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2372.6</v>
+        <v>2373.4</v>
       </c>
     </row>
     <row r="30">
@@ -43052,7 +43052,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.92</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="32">
@@ -43062,7 +43062,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/017960_model.xlsx
+++ b/argus/kship/models/017960_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 185386억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 185456억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 193895억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 194009억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 194492억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 194592억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 200790억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 200832억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 209407억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 209288억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 220555억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 220283억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 228588억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 228213억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 233324억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
+고객지수 4분기 이동합(t−1) 232896억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 185386억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 185456억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 193895억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 194009억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 194492억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 194592억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 200790억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 200832억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 209407억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 209288억 × 비례계수 0.0672 × 계절비중 Q1 0.222(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 220555억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 220283억 × 비례계수 0.0672 × 계절비중 Q2 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 228588억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 228213억 × 비례계수 0.0672 × 계절비중 Q3 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 233324억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−1) 232896억 × 비례계수 0.0672 × 계절비중 Q4 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=15, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2154,13 +2154,13 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3031억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3032억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3430억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기 중위 -40.74억이 이자손익 추정 -10.23억의 50% 초과 → 0(경고)) (항등식); 이자손익 = 이자발생자산 3431억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2214,13 +2214,13 @@
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3031억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3032억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3430억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3431억 × 1.97%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1413억 × 5.19%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 1.98% / 부채 5.19% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0197, 0.0519] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
+          <t>· 이자율 자산 1.97% / 부채 5.19% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0197, 0.0519] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5652,35 +5652,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5771,35 +5771,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5890,35 +5890,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6009,35 +6009,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6128,35 +6128,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6263,7 +6263,7 @@
         <v>20100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18190</v>
+        <v>15420</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6445,7 +6445,7 @@
         <v>18530</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>17220</v>
+        <v>15390</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6536,7 +6536,7 @@
         <v>22833.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19117.3</v>
+        <v>18288.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6695,29 +6695,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.307105028</v>
+        <v>0.307605449</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.323132945</v>
+        <v>0.323905407</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.203925607</v>
+        <v>0.204545796</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.147498213</v>
+        <v>0.147742435</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.129575654</v>
+        <v>0.128504327</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.137494139</v>
+        <v>0.13543073</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.17530643</v>
+        <v>0.172769739</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.162031125</v>
+        <v>0.15965342</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7009,32 +7009,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.137673229</v>
+        <v>0.137674697</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.137674251</v>
+        <v>0.137674615</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.137673196</v>
+        <v>0.137674082</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.137675066</v>
+        <v>0.137674315</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.137672702</v>
+        <v>0.13767388</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.137675165</v>
+        <v>0.137672682</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.137674557</v>
+        <v>0.137675144</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.137673326</v>
+        <v>0.137673392</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8504,36 +8504,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.006100722</v>
+        <v>-0.006835096</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.000547042</v>
+        <v>-0.001872716</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.003626296</v>
+        <v>-0.00163233</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>165.363701638</v>
+        <v>165.358809343</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-9.3891e-05</v>
+        <v>0.002849881</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.000769446</v>
+        <v>-0.007027667</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.005071874</v>
+        <v>0.002526361</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>165.370207399</v>
+        <v>165.361573288</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.003423587</v>
+        <v>-0.003668215</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.001491496</v>
+        <v>-0.003552865</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8632,36 +8632,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>-0.006100722</v>
+        <v>-0.006835096</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.000547042</v>
+        <v>-0.001872716</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.003626296</v>
+        <v>-0.00163233</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>165.363701638</v>
+        <v>165.358809343</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>-9.3891e-05</v>
+        <v>0.002849881</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>0.000769446</v>
+        <v>-0.007027667</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.005071874</v>
+        <v>0.002526361</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>165.370207399</v>
+        <v>165.361573288</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>0.003423587</v>
+        <v>-0.003668215</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.001491496</v>
+        <v>-0.003552865</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8895,29 +8895,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.47389222</v>
+        <v>0.474076431</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.188269781</v>
+        <v>0.188473467</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.315446253</v>
+        <v>0.31551528</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.289877301</v>
+        <v>0.289841593</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.183008267</v>
+        <v>0.182842463</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.10306489</v>
+        <v>0.102827151</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.169764469</v>
+        <v>0.169489622</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.173066345</v>
+        <v>0.172795421</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9023,29 +9023,29 @@
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>0.125615895</v>
+        <v>0.125664722</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.06534401200000001</v>
+        <v>0.065416101</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.122113189</v>
+        <v>0.122166252</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.131556377</v>
+        <v>0.131561935</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.09467086500000001</v>
+        <v>0.09460586</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.057620095</v>
+        <v>0.057488956</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.09898773700000001</v>
+        <v>0.098826053</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.107411998</v>
+        <v>0.107235178</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9708,11 +9708,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>18190</v>
+        <v>15420</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 17,550원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,820원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.243561257414456</v>
+        <v>0.2435642458580504</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.09507496555945608</v>
+        <v>0.09507472479233983</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.01975282745898116</v>
+        <v>0.01974692920334247</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.05187997566164976</v>
+        <v>0.05187189533369108</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35435,7 +35435,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40824,7 +40824,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43032,7 +43032,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2373.4</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="30">
@@ -43052,7 +43052,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.66</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="32">
@@ -43062,7 +43062,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="33">
@@ -43072,7 +43072,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1821</v>
+        <v>0.1822</v>
       </c>
     </row>
     <row r="34">
